--- a/images/stx_fish_image_schema_main_v0.1.xlsx
+++ b/images/stx_fish_image_schema_main_v0.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/providen/Documents/EI/Projects/COPO-schemas/images/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74047299-6222-054F-876F-C79105C4FDA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D215CBE6-07FA-1D44-8A6B-A6890E63F3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17960" xr2:uid="{7BD8D0E6-E1F4-E04F-9790-31602B31B6DB}"/>
+    <workbookView xWindow="32740" yWindow="-940" windowWidth="30240" windowHeight="17900" xr2:uid="{7BD8D0E6-E1F4-E04F-9790-31602B31B6DB}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="413">
   <si>
     <t>component_name</t>
   </si>
@@ -149,15 +149,9 @@
     <t>A unique alphanumeric identifier for this study</t>
   </si>
   <si>
-    <t>A7F9B3X2</t>
-  </si>
-  <si>
     <t>^[a-zA-Z0-9]+$</t>
   </si>
   <si>
-    <t>Only letters and numbers allowed. No spaces or special characters.</t>
-  </si>
-  <si>
     <t>single</t>
   </si>
   <si>
@@ -182,9 +176,6 @@
     <t>A name given to the study or project. Project title should be fewer than 30 words, such as a title of a grant proposal or a publication.</t>
   </si>
   <si>
-    <t>Study of single cells in the human body</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -407,9 +398,6 @@
     <t>A unique alphanumeric reference or identifier for the sample. This field must provide a consistent, unambiguous way to identify the sample within and across datasets. It can be a name, code, or accession-like format, as long as it remains unique.</t>
   </si>
   <si>
-    <t>sample123</t>
-  </si>
-  <si>
     <t>scientific_name</t>
   </si>
   <si>
@@ -425,9 +413,6 @@
     <t>Salvelinus alpinus</t>
   </si>
   <si>
-    <t>String must start with uppercase and contain at least one lowercase letter.</t>
-  </si>
-  <si>
     <t>BIOSAMPLEACCESSION_EXT_FIELD</t>
   </si>
   <si>
@@ -446,9 +431,6 @@
     <t>^[0-9]+$</t>
   </si>
   <si>
-    <t>It must be numbers</t>
-  </si>
-  <si>
     <t>http://rs.tdwg.org/dwc/terms/taxonID</t>
   </si>
   <si>
@@ -542,9 +524,6 @@
     <t>A unique alphanumeric identifier for the imaging protocol.</t>
   </si>
   <si>
-    <t>img123</t>
-  </si>
-  <si>
     <t>platform</t>
   </si>
   <si>
@@ -704,9 +683,6 @@
     <t>The guide used for sample preparation.</t>
   </si>
   <si>
-    <t>preparation_guide_v1.0.pdf</t>
-  </si>
-  <si>
     <t>^[A-Za-z0-9._-]*[a-z]+$</t>
   </si>
   <si>
@@ -749,22 +725,10 @@
     <t>File Name</t>
   </si>
   <si>
-    <t>A filename or file name is a name used to uniquely identify a data file related to the study.</t>
-  </si>
-  <si>
-    <t>file001</t>
-  </si>
-  <si>
     <t>file_type</t>
   </si>
   <si>
     <t>File Type</t>
-  </si>
-  <si>
-    <t>A file type is a name given to a specific kind of file. Common file types are fastq, gtf, fasta, bam, archive etc.</t>
-  </si>
-  <si>
-    <t>fastq</t>
   </si>
   <si>
     <t>sex</t>
@@ -1392,12 +1356,51 @@
   <si>
     <t>Tree of Life metadata</t>
   </si>
+  <si>
+    <t>STUDY001</t>
+  </si>
+  <si>
+    <t>SAMP001</t>
+  </si>
+  <si>
+    <t>IMGPRO001</t>
+  </si>
+  <si>
+    <t>FILE001</t>
+  </si>
+  <si>
+    <t>example_guide_v1.0.pdf</t>
+  </si>
+  <si>
+    <t>Expected letters and numbers only with no spaces or special characters.</t>
+  </si>
+  <si>
+    <t>Expected a text that starts with an uppercase letter and contains at least one lowercase letter.</t>
+  </si>
+  <si>
+    <t>Expected positive whole numbers only.</t>
+  </si>
+  <si>
+    <t>Spatial Transcriptomics FISH of Human Lung Tissue</t>
+  </si>
+  <si>
+    <t>file001.tiff</t>
+  </si>
+  <si>
+    <t>tiff</t>
+  </si>
+  <si>
+    <t>A file name  is  used to uniquely identify a data file related to the study.  Common file names end with  tiff, jpeg, png, gif, bmp and ome-tiff etc.</t>
+  </si>
+  <si>
+    <t>A file type is a name given to a specific kind of file. Common file types are tiff, jpeg, png, gif, bmp and ome-tiff etc.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1486,6 +1489,13 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1519,7 +1529,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -1639,28 +1649,6 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1869,34 +1857,6 @@
       <top style="thick">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -1913,36 +1873,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -1988,12 +1918,125 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2074,9 +2117,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2091,19 +2131,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2118,19 +2152,28 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2142,28 +2185,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2175,14 +2200,53 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2604,7 +2668,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="H1" s="14" t="s">
         <v>6</v>
@@ -2630,10 +2694,10 @@
       <c r="O1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="58" t="s">
+      <c r="P1" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="50" t="s">
+      <c r="Q1" s="48" t="s">
         <v>15</v>
       </c>
       <c r="R1" s="26" t="s">
@@ -2660,29 +2724,29 @@
         <v>21</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="K2" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="62" t="s">
+        <v>405</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="O2" s="3"/>
+      <c r="P2" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" s="3"/>
-      <c r="P2" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="R2" s="46" t="s">
-        <v>27</v>
+      <c r="Q2" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2" s="44" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="16" x14ac:dyDescent="0.2">
@@ -2690,45 +2754,45 @@
         <v>17</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F3" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>33</v>
+        <v>408</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="Q3" s="50"/>
+      <c r="R3" s="38" t="s">
         <v>26</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="P3" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q3" s="52"/>
-      <c r="R3" s="39" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="16" x14ac:dyDescent="0.2">
@@ -2736,42 +2800,42 @@
         <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F4" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>33</v>
+        <v>408</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="R4" s="39"/>
+      <c r="R4" s="38"/>
     </row>
     <row r="5" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
@@ -2781,37 +2845,37 @@
         <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F5" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>46</v>
+        <v>229</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N5" s="10" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O5" s="3"/>
-      <c r="P5" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q5" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="R5" s="39" t="s">
-        <v>28</v>
+      <c r="P5" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="R5" s="38" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -2822,42 +2886,42 @@
         <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F6" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="J6" t="s">
-        <v>58</v>
+        <v>389</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N6" s="10" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O6" s="4"/>
-      <c r="P6" s="43" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q6" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="R6" s="48" t="s">
-        <v>28</v>
+      <c r="P6" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q6" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="R6" s="46" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>18</v>
@@ -2873,364 +2937,356 @@
         <v>0</v>
       </c>
       <c r="G7" s="7"/>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="63" t="s">
+        <v>400</v>
+      </c>
+      <c r="K7" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="L7" s="68" t="s">
+        <v>405</v>
+      </c>
+      <c r="M7" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="N7" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="O7" s="69"/>
+      <c r="P7" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q7" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="R7" s="30" t="s">
-        <v>27</v>
+      <c r="Q7" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="R7" s="66" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F8" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="M8" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O8" s="3"/>
+      <c r="P8" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="O8" s="3"/>
-      <c r="P8" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q8" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="R8" s="47" t="s">
-        <v>28</v>
+      <c r="Q8" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="R8" s="45" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F9" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O9" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="M9" s="3" t="s">
+      <c r="P9" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="P9" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q9" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="R9" s="39" t="s">
-        <v>27</v>
+      <c r="Q9" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="R9" s="38" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F10" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I10" t="s">
+        <v>72</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O10" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="M10" s="3" t="s">
+      <c r="P10" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="P10" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q10" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="R10" s="39" t="s">
-        <v>27</v>
+      <c r="Q10" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="R10" s="38" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F11" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J11" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J11" s="25" t="s">
+      <c r="M11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O11" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N11" s="3" t="s">
+      <c r="P11" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="O11" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="P11" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q11" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="R11" s="39" t="s">
-        <v>28</v>
+      <c r="Q11" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="R11" s="38" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F12" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I12" t="s">
+        <v>85</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O12" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="M12" s="3" t="s">
+      <c r="P12" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O12" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="P12" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q12" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="R12" s="39" t="s">
-        <v>27</v>
+      <c r="Q12" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="R12" s="38" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F13" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="P13" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="O13" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="P13" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q13" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="R13" s="39" t="s">
-        <v>28</v>
+      <c r="Q13" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="R13" s="38" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F14" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I14" t="s">
+        <v>96</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O14" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N14" s="3" t="s">
+      <c r="P14" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="O14" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="P14" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q14" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="R14" s="47" t="s">
-        <v>28</v>
+      <c r="Q14" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="R14" s="45" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>18</v>
@@ -3250,228 +3306,224 @@
         <v>17</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="J15" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="K15" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="L15" s="68" t="s">
+        <v>405</v>
+      </c>
+      <c r="M15" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="N15" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="O15" s="63"/>
+      <c r="P15" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="N15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O15" s="2"/>
-      <c r="P15" s="59" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q15" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="R15" s="30" t="s">
-        <v>27</v>
+      <c r="Q15" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="R15" s="66" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F16" s="1" t="b">
         <v>1</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="K16" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L16" s="3" t="s">
+      <c r="N16" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M16" s="3" t="s">
+      <c r="O16" s="3"/>
+      <c r="P16" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="N16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O16" s="3"/>
-      <c r="P16" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q16" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="R16" s="39" t="s">
-        <v>27</v>
+      <c r="Q16" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="R16" s="38" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F17" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>114</v>
+        <v>406</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="P17" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q17" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="R17" s="39" t="s">
-        <v>28</v>
+        <v>111</v>
+      </c>
+      <c r="P17" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q17" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="R17" s="38" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F18" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J18" s="3">
         <v>8036</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>121</v>
+        <v>407</v>
       </c>
       <c r="M18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="P18" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="O18" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="P18" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q18" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="R18" s="60" t="s">
-        <v>27</v>
+      <c r="Q18" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="R18" s="55" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="F19" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="P19" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="N19" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="O19" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="P19" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q19" s="56" t="s">
-        <v>27</v>
-      </c>
-      <c r="R19" s="61" t="s">
-        <v>27</v>
+      <c r="Q19" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="R19" s="71" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>18</v>
@@ -3494,709 +3546,697 @@
         <v>21</v>
       </c>
       <c r="J20" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="K20" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="L20" s="68" t="s">
+        <v>405</v>
+      </c>
+      <c r="M20" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="L20" s="2" t="s">
+      <c r="N20" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="O20" s="63"/>
+      <c r="P20" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="N20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O20" s="2"/>
-      <c r="P20" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q20" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="R20" s="49" t="s">
-        <v>27</v>
+      <c r="Q20" s="73" t="s">
+        <v>25</v>
+      </c>
+      <c r="R20" s="74" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="F21" s="1" t="b">
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="K21" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L21" s="3" t="s">
+      <c r="N21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M21" s="3" t="s">
+      <c r="O21" s="3"/>
+      <c r="P21" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O21" s="3"/>
-      <c r="P21" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q21" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="R21" s="39" t="s">
-        <v>27</v>
+      <c r="Q21" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="R21" s="38" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="F22" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="K22" s="3"/>
-      <c r="L22" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="L22" s="3"/>
       <c r="M22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O22" s="3"/>
+      <c r="P22" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O22" s="3"/>
-      <c r="P22" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q22" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="R22" s="39" t="s">
-        <v>27</v>
+      <c r="Q22" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="R22" s="38" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="F23" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="K23" s="3"/>
-      <c r="L23" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O23" s="3"/>
+      <c r="P23" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O23" s="3"/>
-      <c r="P23" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q23" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="R23" s="39" t="s">
-        <v>27</v>
+      <c r="Q23" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="R23" s="38" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="F24" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="K24" s="3"/>
-      <c r="L24" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="L24" s="3"/>
       <c r="M24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O24" s="3"/>
+      <c r="P24" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O24" s="3"/>
-      <c r="P24" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q24" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="R24" s="39" t="s">
-        <v>27</v>
+      <c r="Q24" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="R24" s="38" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="F25" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="L25" s="16" t="s">
-        <v>169</v>
+        <v>161</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O25" s="3"/>
+      <c r="P25" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="O25" s="3"/>
-      <c r="P25" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q25" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="R25" s="39" t="s">
-        <v>28</v>
+      <c r="Q25" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="R25" s="38" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F26" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="K26" s="3"/>
-      <c r="L26" s="3" t="s">
-        <v>51</v>
-      </c>
+      <c r="L26" s="3"/>
       <c r="M26" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O26" s="3"/>
+      <c r="P26" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="O26" s="3"/>
-      <c r="P26" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q26" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="R26" s="39" t="s">
-        <v>28</v>
+      <c r="Q26" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="R26" s="38" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F27" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="J27" s="3">
         <v>22</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O27" s="3"/>
+      <c r="P27" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="O27" s="3"/>
-      <c r="P27" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q27" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="R27" s="39" t="s">
-        <v>28</v>
+      <c r="Q27" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="R27" s="38" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F28" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N28" s="10" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O28" s="3"/>
-      <c r="P28" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q28" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="R28" s="39" t="s">
-        <v>28</v>
+      <c r="P28" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q28" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="R28" s="38" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F29" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="M29" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O29" s="3"/>
+      <c r="P29" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="O29" s="3"/>
-      <c r="P29" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q29" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="R29" s="39" t="s">
-        <v>28</v>
+      <c r="Q29" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="R29" s="38" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F30" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="M30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O30" s="3"/>
+      <c r="P30" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="N30" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O30" s="3"/>
-      <c r="P30" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q30" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="R30" s="39" t="s">
-        <v>27</v>
+      <c r="Q30" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="R30" s="38" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F31" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="M31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O31" s="3"/>
+      <c r="P31" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="N31" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O31" s="3"/>
-      <c r="P31" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q31" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="R31" s="39" t="s">
-        <v>27</v>
+      <c r="Q31" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="R31" s="38" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F32" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O32" s="3"/>
+      <c r="P32" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O32" s="3"/>
-      <c r="P32" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q32" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="R32" s="39" t="s">
-        <v>27</v>
+      <c r="Q32" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="R32" s="38" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="F33" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="L33" s="16" t="s">
-        <v>169</v>
+        <v>161</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="M33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O33" s="3"/>
+      <c r="P33" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O33" s="3"/>
-      <c r="P33" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q33" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="R33" s="39" t="s">
-        <v>27</v>
+      <c r="Q33" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="R33" s="38" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="F34" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>207</v>
+        <v>404</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O34" s="3"/>
+      <c r="P34" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="N34" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O34" s="3"/>
-      <c r="P34" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q34" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="R34" s="39" t="s">
-        <v>27</v>
+      <c r="Q34" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="R34" s="38" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="9" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="F35" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="L35" s="16" t="s">
-        <v>169</v>
+        <v>161</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>162</v>
       </c>
       <c r="M35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O35" s="3"/>
+      <c r="P35" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O35" s="3"/>
-      <c r="P35" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q35" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="R35" s="39" t="s">
-        <v>27</v>
+      <c r="Q35" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="R35" s="38" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="8" t="b">
@@ -4205,33 +4245,33 @@
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
       <c r="I36" s="5" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="K36" s="5"/>
       <c r="L36" s="3"/>
       <c r="M36" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N36" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="O36" s="5"/>
+      <c r="P36" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="N36" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q36" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="R36" s="47" t="s">
-        <v>27</v>
+      <c r="Q36" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="R36" s="45" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:18" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>18</v>
@@ -4254,213 +4294,201 @@
         <v>21</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K37" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L37" s="2" t="s">
+      <c r="N37" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M37" s="2" t="s">
+      <c r="O37" s="2"/>
+      <c r="P37" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="N37" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O37" s="2"/>
-      <c r="P37" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q37" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="R37" s="49" t="s">
-        <v>27</v>
+      <c r="Q37" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="R37" s="47" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F38" s="1" t="b">
         <v>1</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K38" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L38" s="3" t="s">
+      <c r="N38" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M38" s="3" t="s">
+      <c r="O38" s="3"/>
+      <c r="P38" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="N38" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O38" s="3"/>
-      <c r="P38" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q38" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="R38" s="39" t="s">
-        <v>27</v>
+      <c r="Q38" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="R38" s="38" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="9" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="F39" s="1" t="b">
         <v>0</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="K39" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="M39" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="L39" s="3" t="s">
+      <c r="N39" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M39" s="3" t="s">
+      <c r="O39" s="3"/>
+      <c r="P39" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="N39" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O39" s="3"/>
-      <c r="P39" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q39" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="R39" s="39" t="s">
-        <v>27</v>
+      <c r="Q39" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="R39" s="38" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="9" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="F40" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>222</v>
+        <v>411</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>223</v>
+        <v>409</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="O40" s="3"/>
+      <c r="P40" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="N40" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="O40" s="3"/>
-      <c r="P40" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q40" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="R40" s="39" t="s">
-        <v>27</v>
+      <c r="Q40" s="50" t="s">
+        <v>25</v>
+      </c>
+      <c r="R40" s="38" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="9" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="F41" s="1" t="b">
         <v>0</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>226</v>
+        <v>412</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>227</v>
+        <v>410</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O41" s="3"/>
+      <c r="P41" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="O41" s="3"/>
-      <c r="P41" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q41" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="R41" s="47" t="s">
-        <v>27</v>
+      <c r="Q41" s="51" t="s">
+        <v>25</v>
+      </c>
+      <c r="R41" s="45" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:R41" xr:uid="{545CA0C1-0282-3A43-9C60-512DE414A571}"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P40:R41 P2:R39" xr:uid="{D3C8CE10-E7EB-B24A-855C-B8189CB5A06C}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:R41" xr:uid="{D3C8CE10-E7EB-B24A-855C-B8189CB5A06C}"/>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="O3" r:id="rId1" xr:uid="{4D6B5FE8-0E6D-E84F-B3F9-D5B11E30DF9B}"/>
@@ -4490,2341 +4518,2341 @@
   <cols>
     <col min="1" max="1" width="35.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5" customWidth="1"/>
-    <col min="3" max="3" width="61.1640625" style="36" customWidth="1"/>
+    <col min="3" max="3" width="61.1640625" style="35" customWidth="1"/>
     <col min="4" max="4" width="22.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="15" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="60" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1" s="61" t="s">
+        <v>384</v>
+      </c>
+      <c r="D1" s="61" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="66" t="s">
-        <v>179</v>
-      </c>
-      <c r="C1" s="67" t="s">
-        <v>396</v>
-      </c>
-      <c r="D1" s="67" t="s">
+      <c r="B2" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="56" t="s">
+        <v>217</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="C3" s="56" t="s">
+        <v>219</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="B4" s="32"/>
+      <c r="C4" s="56" t="s">
+        <v>221</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="B5" s="32"/>
+      <c r="C5" s="56" t="s">
+        <v>223</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="B6" s="32"/>
+      <c r="C6" s="56" t="s">
+        <v>225</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="32" t="s">
+        <v>226</v>
+      </c>
+      <c r="B7" s="32"/>
+      <c r="C7" s="56" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="C2" s="62" t="s">
+      <c r="D7" s="33" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="B8" s="32"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="33"/>
+    </row>
+    <row r="9" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="32" t="s">
         <v>229</v>
       </c>
-      <c r="D2" s="34" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="33" t="s">
-        <v>230</v>
-      </c>
-      <c r="B3" s="33" t="s">
-        <v>182</v>
-      </c>
-      <c r="C3" s="62" t="s">
-        <v>231</v>
-      </c>
-      <c r="D3" s="34" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="62" t="s">
-        <v>233</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="62" t="s">
-        <v>235</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="33" t="s">
-        <v>236</v>
-      </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="62" t="s">
-        <v>237</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="33" t="s">
-        <v>238</v>
-      </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="62" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="33" t="s">
-        <v>240</v>
-      </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="62"/>
-      <c r="D8" s="34"/>
-    </row>
-    <row r="9" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="33" t="s">
-        <v>241</v>
-      </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="34"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="33"/>
     </row>
     <row r="10" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="33"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="62"/>
-      <c r="D10" s="34"/>
+      <c r="A10" s="32"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="33"/>
     </row>
     <row r="11" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="33"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="62"/>
-      <c r="D11" s="34"/>
+      <c r="A11" s="32"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="33"/>
     </row>
     <row r="12" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A12" s="33"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="34"/>
+      <c r="A12" s="32"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="56"/>
+      <c r="D12" s="33"/>
     </row>
     <row r="13" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="33"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="34"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="33"/>
     </row>
     <row r="14" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="33"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="62"/>
-      <c r="D14" s="34"/>
+      <c r="A14" s="32"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="33"/>
     </row>
     <row r="15" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="33"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="34"/>
+      <c r="A15" s="32"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="33"/>
     </row>
     <row r="16" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="33"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="62"/>
-      <c r="D16" s="34"/>
+      <c r="A16" s="32"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="56"/>
+      <c r="D16" s="33"/>
     </row>
     <row r="17" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="33"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="62"/>
-      <c r="D17" s="34"/>
+      <c r="A17" s="32"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="33"/>
     </row>
     <row r="18" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="33"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="62"/>
-      <c r="D18" s="34"/>
+      <c r="A18" s="32"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="33"/>
     </row>
     <row r="19" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" s="33"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="62"/>
-      <c r="D19" s="34"/>
+      <c r="A19" s="32"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="33"/>
     </row>
     <row r="20" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="33"/>
-      <c r="B20" s="33"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="34"/>
+      <c r="A20" s="32"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="33"/>
     </row>
     <row r="21" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="33"/>
-      <c r="B21" s="33"/>
-      <c r="C21" s="62"/>
-      <c r="D21" s="34"/>
+      <c r="A21" s="32"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="56"/>
+      <c r="D21" s="33"/>
     </row>
     <row r="22" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="33"/>
-      <c r="B22" s="33"/>
-      <c r="C22" s="62"/>
-      <c r="D22" s="34"/>
+      <c r="A22" s="32"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="56"/>
+      <c r="D22" s="33"/>
     </row>
     <row r="23" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" s="33"/>
-      <c r="B23" s="33"/>
-      <c r="C23" s="63"/>
-      <c r="D23" s="34"/>
+      <c r="A23" s="32"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="33"/>
     </row>
     <row r="24" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A24" s="33"/>
-      <c r="B24" s="33"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="34"/>
+      <c r="A24" s="32"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="33"/>
     </row>
     <row r="25" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" s="33"/>
-      <c r="B25" s="33"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="34"/>
+      <c r="A25" s="32"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="33"/>
     </row>
     <row r="26" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A26" s="33"/>
-      <c r="B26" s="33"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="34"/>
+      <c r="A26" s="32"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="33"/>
     </row>
     <row r="27" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A27" s="33"/>
-      <c r="B27" s="33"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="34"/>
+      <c r="A27" s="32"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="56"/>
+      <c r="D27" s="33"/>
     </row>
     <row r="28" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" s="33"/>
-      <c r="B28" s="33"/>
-      <c r="C28" s="62"/>
-      <c r="D28" s="34"/>
+      <c r="A28" s="32"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="33"/>
     </row>
     <row r="29" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" s="33"/>
-      <c r="B29" s="33"/>
-      <c r="C29" s="62"/>
-      <c r="D29" s="34"/>
+      <c r="A29" s="32"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="56"/>
+      <c r="D29" s="33"/>
     </row>
     <row r="30" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A30" s="33"/>
-      <c r="B30" s="33"/>
-      <c r="C30" s="62"/>
-      <c r="D30" s="34"/>
+      <c r="A30" s="32"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="56"/>
+      <c r="D30" s="33"/>
     </row>
     <row r="31" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A31" s="33"/>
-      <c r="B31" s="33"/>
-      <c r="C31" s="62"/>
-      <c r="D31" s="34"/>
+      <c r="A31" s="32"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="56"/>
+      <c r="D31" s="33"/>
     </row>
     <row r="32" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="33"/>
-      <c r="B32" s="33"/>
-      <c r="C32" s="62"/>
-      <c r="D32" s="34"/>
+      <c r="A32" s="32"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="33"/>
     </row>
     <row r="33" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="33"/>
-      <c r="B33" s="33"/>
-      <c r="C33" s="62"/>
-      <c r="D33" s="34"/>
+      <c r="A33" s="32"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="33"/>
     </row>
     <row r="34" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A34" s="33"/>
-      <c r="B34" s="33"/>
-      <c r="C34" s="62"/>
-      <c r="D34" s="34"/>
+      <c r="A34" s="32"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="33"/>
     </row>
     <row r="35" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" s="33"/>
-      <c r="B35" s="33"/>
-      <c r="C35" s="62"/>
-      <c r="D35" s="34"/>
+      <c r="A35" s="32"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="33"/>
     </row>
     <row r="36" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="33"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="62"/>
-      <c r="D36" s="34"/>
+      <c r="A36" s="32"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="56"/>
+      <c r="D36" s="33"/>
     </row>
     <row r="37" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A37" s="33"/>
-      <c r="B37" s="33"/>
-      <c r="C37" s="62"/>
-      <c r="D37" s="34"/>
+      <c r="A37" s="32"/>
+      <c r="B37" s="32"/>
+      <c r="C37" s="56"/>
+      <c r="D37" s="33"/>
     </row>
     <row r="38" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="33"/>
-      <c r="B38" s="33"/>
-      <c r="C38" s="62"/>
-      <c r="D38" s="34"/>
+      <c r="A38" s="32"/>
+      <c r="B38" s="32"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="33"/>
     </row>
     <row r="39" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="33"/>
-      <c r="B39" s="33"/>
-      <c r="C39" s="62"/>
-      <c r="D39" s="34"/>
+      <c r="A39" s="32"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="56"/>
+      <c r="D39" s="33"/>
     </row>
     <row r="40" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="33"/>
-      <c r="B40" s="33"/>
-      <c r="C40" s="62"/>
-      <c r="D40" s="34"/>
+      <c r="A40" s="32"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="33"/>
     </row>
     <row r="41" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="33"/>
-      <c r="B41" s="33"/>
-      <c r="C41" s="62"/>
-      <c r="D41" s="34"/>
+      <c r="A41" s="32"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="56"/>
+      <c r="D41" s="33"/>
     </row>
     <row r="42" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" s="33"/>
-      <c r="B42" s="33"/>
-      <c r="C42" s="62"/>
-      <c r="D42" s="34"/>
+      <c r="A42" s="32"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="56"/>
+      <c r="D42" s="33"/>
     </row>
     <row r="43" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A43" s="33"/>
-      <c r="B43" s="33"/>
-      <c r="C43" s="62"/>
-      <c r="D43" s="34"/>
+      <c r="A43" s="32"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="56"/>
+      <c r="D43" s="33"/>
     </row>
     <row r="44" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="33"/>
-      <c r="B44" s="33"/>
-      <c r="C44" s="62"/>
-      <c r="D44" s="34"/>
+      <c r="A44" s="32"/>
+      <c r="B44" s="32"/>
+      <c r="C44" s="56"/>
+      <c r="D44" s="33"/>
     </row>
     <row r="45" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="33"/>
-      <c r="B45" s="33"/>
-      <c r="C45" s="62"/>
-      <c r="D45" s="34"/>
+      <c r="A45" s="32"/>
+      <c r="B45" s="32"/>
+      <c r="C45" s="56"/>
+      <c r="D45" s="33"/>
     </row>
     <row r="46" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A46" s="33"/>
-      <c r="B46" s="33"/>
-      <c r="C46" s="62"/>
-      <c r="D46" s="34"/>
+      <c r="A46" s="32"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="56"/>
+      <c r="D46" s="33"/>
     </row>
     <row r="47" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="33"/>
-      <c r="B47" s="33"/>
-      <c r="C47" s="62"/>
-      <c r="D47" s="34"/>
+      <c r="A47" s="32"/>
+      <c r="B47" s="32"/>
+      <c r="C47" s="56"/>
+      <c r="D47" s="33"/>
     </row>
     <row r="48" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="33"/>
-      <c r="B48" s="33"/>
-      <c r="C48" s="62"/>
-      <c r="D48" s="34"/>
+      <c r="A48" s="32"/>
+      <c r="B48" s="32"/>
+      <c r="C48" s="56"/>
+      <c r="D48" s="33"/>
     </row>
     <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A49" s="33"/>
-      <c r="B49" s="33"/>
-      <c r="C49" s="62"/>
-      <c r="D49" s="34"/>
+      <c r="A49" s="32"/>
+      <c r="B49" s="32"/>
+      <c r="C49" s="56"/>
+      <c r="D49" s="33"/>
     </row>
     <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="33"/>
-      <c r="B50" s="33"/>
-      <c r="C50" s="62"/>
-      <c r="D50" s="34"/>
+      <c r="A50" s="32"/>
+      <c r="B50" s="32"/>
+      <c r="C50" s="56"/>
+      <c r="D50" s="33"/>
     </row>
     <row r="51" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A51" s="33"/>
-      <c r="B51" s="33"/>
-      <c r="C51" s="62"/>
-      <c r="D51" s="34"/>
+      <c r="A51" s="32"/>
+      <c r="B51" s="32"/>
+      <c r="C51" s="56"/>
+      <c r="D51" s="33"/>
     </row>
     <row r="52" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A52" s="33"/>
-      <c r="B52" s="33"/>
-      <c r="C52" s="62"/>
-      <c r="D52" s="34"/>
+      <c r="A52" s="32"/>
+      <c r="B52" s="32"/>
+      <c r="C52" s="56"/>
+      <c r="D52" s="33"/>
     </row>
     <row r="53" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A53" s="33"/>
-      <c r="B53" s="33"/>
-      <c r="C53" s="62"/>
-      <c r="D53" s="34"/>
+      <c r="A53" s="32"/>
+      <c r="B53" s="32"/>
+      <c r="C53" s="56"/>
+      <c r="D53" s="33"/>
     </row>
     <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A54" s="33"/>
-      <c r="B54" s="33"/>
-      <c r="C54" s="62"/>
-      <c r="D54" s="34"/>
+      <c r="A54" s="32"/>
+      <c r="B54" s="32"/>
+      <c r="C54" s="56"/>
+      <c r="D54" s="33"/>
     </row>
     <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A55" s="33"/>
-      <c r="B55" s="33"/>
-      <c r="C55" s="62"/>
-      <c r="D55" s="34"/>
+      <c r="A55" s="32"/>
+      <c r="B55" s="32"/>
+      <c r="C55" s="56"/>
+      <c r="D55" s="33"/>
     </row>
     <row r="56" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A56" s="33"/>
-      <c r="B56" s="33"/>
-      <c r="C56" s="62"/>
-      <c r="D56" s="34"/>
+      <c r="A56" s="32"/>
+      <c r="B56" s="32"/>
+      <c r="C56" s="56"/>
+      <c r="D56" s="33"/>
     </row>
     <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A57" s="33"/>
-      <c r="B57" s="33"/>
-      <c r="C57" s="62"/>
-      <c r="D57" s="34"/>
+      <c r="A57" s="32"/>
+      <c r="B57" s="32"/>
+      <c r="C57" s="56"/>
+      <c r="D57" s="33"/>
     </row>
     <row r="58" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A58" s="33"/>
-      <c r="B58" s="33"/>
-      <c r="C58" s="62"/>
-      <c r="D58" s="34"/>
+      <c r="A58" s="32"/>
+      <c r="B58" s="32"/>
+      <c r="C58" s="56"/>
+      <c r="D58" s="33"/>
     </row>
     <row r="59" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A59" s="33"/>
-      <c r="B59" s="33"/>
-      <c r="C59" s="62"/>
-      <c r="D59" s="34"/>
+      <c r="A59" s="32"/>
+      <c r="B59" s="32"/>
+      <c r="C59" s="56"/>
+      <c r="D59" s="33"/>
     </row>
     <row r="60" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A60" s="33"/>
-      <c r="B60" s="33"/>
-      <c r="C60" s="62"/>
-      <c r="D60" s="34"/>
+      <c r="A60" s="32"/>
+      <c r="B60" s="32"/>
+      <c r="C60" s="56"/>
+      <c r="D60" s="33"/>
     </row>
     <row r="61" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A61" s="33"/>
-      <c r="B61" s="33"/>
-      <c r="C61" s="62"/>
-      <c r="D61" s="34"/>
+      <c r="A61" s="32"/>
+      <c r="B61" s="32"/>
+      <c r="C61" s="56"/>
+      <c r="D61" s="33"/>
     </row>
     <row r="62" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A62" s="33"/>
-      <c r="B62" s="33"/>
-      <c r="C62" s="62"/>
-      <c r="D62" s="34"/>
+      <c r="A62" s="32"/>
+      <c r="B62" s="32"/>
+      <c r="C62" s="56"/>
+      <c r="D62" s="33"/>
     </row>
     <row r="63" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A63" s="33"/>
-      <c r="B63" s="33"/>
-      <c r="C63" s="62"/>
-      <c r="D63" s="34"/>
+      <c r="A63" s="32"/>
+      <c r="B63" s="32"/>
+      <c r="C63" s="56"/>
+      <c r="D63" s="33"/>
     </row>
     <row r="64" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A64" s="33"/>
-      <c r="B64" s="33"/>
-      <c r="C64" s="62"/>
-      <c r="D64" s="34"/>
+      <c r="A64" s="32"/>
+      <c r="B64" s="32"/>
+      <c r="C64" s="56"/>
+      <c r="D64" s="33"/>
     </row>
     <row r="65" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A65" s="33"/>
-      <c r="B65" s="33"/>
-      <c r="C65" s="62"/>
-      <c r="D65" s="34"/>
+      <c r="A65" s="32"/>
+      <c r="B65" s="32"/>
+      <c r="C65" s="56"/>
+      <c r="D65" s="33"/>
     </row>
     <row r="66" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A66" s="33"/>
-      <c r="B66" s="33"/>
-      <c r="C66" s="62"/>
-      <c r="D66" s="34"/>
+      <c r="A66" s="32"/>
+      <c r="B66" s="32"/>
+      <c r="C66" s="56"/>
+      <c r="D66" s="33"/>
     </row>
     <row r="67" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A67" s="33"/>
-      <c r="B67" s="33"/>
-      <c r="C67" s="62"/>
-      <c r="D67" s="34"/>
+      <c r="A67" s="32"/>
+      <c r="B67" s="32"/>
+      <c r="C67" s="56"/>
+      <c r="D67" s="33"/>
     </row>
     <row r="68" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A68" s="33"/>
-      <c r="B68" s="33"/>
-      <c r="C68" s="62"/>
-      <c r="D68" s="34"/>
+      <c r="A68" s="32"/>
+      <c r="B68" s="32"/>
+      <c r="C68" s="56"/>
+      <c r="D68" s="33"/>
     </row>
     <row r="69" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A69" s="33"/>
-      <c r="B69" s="33"/>
-      <c r="C69" s="62"/>
-      <c r="D69" s="34"/>
+      <c r="A69" s="32"/>
+      <c r="B69" s="32"/>
+      <c r="C69" s="56"/>
+      <c r="D69" s="33"/>
     </row>
     <row r="70" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A70" s="33"/>
-      <c r="B70" s="33"/>
-      <c r="C70" s="62"/>
-      <c r="D70" s="34"/>
+      <c r="A70" s="32"/>
+      <c r="B70" s="32"/>
+      <c r="C70" s="56"/>
+      <c r="D70" s="33"/>
     </row>
     <row r="71" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A71" s="33"/>
-      <c r="B71" s="33"/>
-      <c r="C71" s="62"/>
-      <c r="D71" s="34"/>
+      <c r="A71" s="32"/>
+      <c r="B71" s="32"/>
+      <c r="C71" s="56"/>
+      <c r="D71" s="33"/>
     </row>
     <row r="72" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A72" s="33"/>
-      <c r="B72" s="33"/>
-      <c r="C72" s="62"/>
-      <c r="D72" s="34"/>
+      <c r="A72" s="32"/>
+      <c r="B72" s="32"/>
+      <c r="C72" s="56"/>
+      <c r="D72" s="33"/>
     </row>
     <row r="73" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A73" s="33"/>
-      <c r="B73" s="33"/>
-      <c r="C73" s="62"/>
-      <c r="D73" s="34"/>
+      <c r="A73" s="32"/>
+      <c r="B73" s="32"/>
+      <c r="C73" s="56"/>
+      <c r="D73" s="33"/>
     </row>
     <row r="74" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A74" s="33"/>
-      <c r="B74" s="33"/>
-      <c r="C74" s="62"/>
-      <c r="D74" s="34"/>
+      <c r="A74" s="32"/>
+      <c r="B74" s="32"/>
+      <c r="C74" s="56"/>
+      <c r="D74" s="33"/>
     </row>
     <row r="75" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A75" s="33"/>
-      <c r="B75" s="33"/>
-      <c r="C75" s="62"/>
-      <c r="D75" s="34"/>
+      <c r="A75" s="32"/>
+      <c r="B75" s="32"/>
+      <c r="C75" s="56"/>
+      <c r="D75" s="33"/>
     </row>
     <row r="76" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="34"/>
-      <c r="B76" s="34"/>
-      <c r="C76" s="62"/>
-      <c r="D76" s="34"/>
+      <c r="A76" s="33"/>
+      <c r="B76" s="33"/>
+      <c r="C76" s="56"/>
+      <c r="D76" s="33"/>
     </row>
     <row r="77" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="34"/>
-      <c r="B77" s="34"/>
-      <c r="C77" s="62"/>
-      <c r="D77" s="34"/>
+      <c r="A77" s="33"/>
+      <c r="B77" s="33"/>
+      <c r="C77" s="56"/>
+      <c r="D77" s="33"/>
     </row>
     <row r="78" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="34"/>
-      <c r="B78" s="34"/>
-      <c r="C78" s="62"/>
-      <c r="D78" s="34"/>
+      <c r="A78" s="33"/>
+      <c r="B78" s="33"/>
+      <c r="C78" s="56"/>
+      <c r="D78" s="33"/>
     </row>
     <row r="79" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="34"/>
-      <c r="B79" s="34"/>
-      <c r="C79" s="62"/>
-      <c r="D79" s="34"/>
+      <c r="A79" s="33"/>
+      <c r="B79" s="33"/>
+      <c r="C79" s="56"/>
+      <c r="D79" s="33"/>
     </row>
     <row r="80" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="34"/>
-      <c r="B80" s="34"/>
-      <c r="C80" s="62"/>
-      <c r="D80" s="34"/>
+      <c r="A80" s="33"/>
+      <c r="B80" s="33"/>
+      <c r="C80" s="56"/>
+      <c r="D80" s="33"/>
     </row>
     <row r="81" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="34"/>
-      <c r="B81" s="34"/>
-      <c r="C81" s="62"/>
-      <c r="D81" s="34"/>
+      <c r="A81" s="33"/>
+      <c r="B81" s="33"/>
+      <c r="C81" s="56"/>
+      <c r="D81" s="33"/>
     </row>
     <row r="82" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="34"/>
-      <c r="B82" s="34"/>
-      <c r="C82" s="62"/>
-      <c r="D82" s="34"/>
+      <c r="A82" s="33"/>
+      <c r="B82" s="33"/>
+      <c r="C82" s="56"/>
+      <c r="D82" s="33"/>
     </row>
     <row r="83" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="34"/>
-      <c r="B83" s="34"/>
-      <c r="C83" s="62"/>
-      <c r="D83" s="34"/>
+      <c r="A83" s="33"/>
+      <c r="B83" s="33"/>
+      <c r="C83" s="56"/>
+      <c r="D83" s="33"/>
     </row>
     <row r="84" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="34"/>
-      <c r="B84" s="34"/>
-      <c r="C84" s="62"/>
-      <c r="D84" s="34"/>
+      <c r="A84" s="33"/>
+      <c r="B84" s="33"/>
+      <c r="C84" s="56"/>
+      <c r="D84" s="33"/>
     </row>
     <row r="85" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="34"/>
-      <c r="B85" s="34"/>
-      <c r="C85" s="62"/>
-      <c r="D85" s="34"/>
+      <c r="A85" s="33"/>
+      <c r="B85" s="33"/>
+      <c r="C85" s="56"/>
+      <c r="D85" s="33"/>
     </row>
     <row r="86" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="34"/>
-      <c r="B86" s="34"/>
-      <c r="C86" s="62"/>
-      <c r="D86" s="34"/>
+      <c r="A86" s="33"/>
+      <c r="B86" s="33"/>
+      <c r="C86" s="56"/>
+      <c r="D86" s="33"/>
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="34"/>
-      <c r="B87" s="34"/>
-      <c r="C87" s="62"/>
-      <c r="D87" s="34"/>
+      <c r="A87" s="33"/>
+      <c r="B87" s="33"/>
+      <c r="C87" s="56"/>
+      <c r="D87" s="33"/>
     </row>
     <row r="88" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="34"/>
-      <c r="B88" s="34"/>
-      <c r="C88" s="62"/>
-      <c r="D88" s="34"/>
+      <c r="A88" s="33"/>
+      <c r="B88" s="33"/>
+      <c r="C88" s="56"/>
+      <c r="D88" s="33"/>
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="34"/>
-      <c r="B89" s="34"/>
-      <c r="C89" s="62"/>
-      <c r="D89" s="34"/>
+      <c r="A89" s="33"/>
+      <c r="B89" s="33"/>
+      <c r="C89" s="56"/>
+      <c r="D89" s="33"/>
     </row>
     <row r="90" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="34"/>
-      <c r="B90" s="34"/>
-      <c r="C90" s="62"/>
-      <c r="D90" s="34"/>
+      <c r="A90" s="33"/>
+      <c r="B90" s="33"/>
+      <c r="C90" s="56"/>
+      <c r="D90" s="33"/>
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="34"/>
-      <c r="B91" s="34"/>
-      <c r="C91" s="62"/>
-      <c r="D91" s="34"/>
+      <c r="A91" s="33"/>
+      <c r="B91" s="33"/>
+      <c r="C91" s="56"/>
+      <c r="D91" s="33"/>
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="34"/>
-      <c r="B92" s="34"/>
-      <c r="C92" s="62"/>
-      <c r="D92" s="34"/>
+      <c r="A92" s="33"/>
+      <c r="B92" s="33"/>
+      <c r="C92" s="56"/>
+      <c r="D92" s="33"/>
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="34"/>
-      <c r="B93" s="34"/>
-      <c r="C93" s="62"/>
-      <c r="D93" s="34"/>
+      <c r="A93" s="33"/>
+      <c r="B93" s="33"/>
+      <c r="C93" s="56"/>
+      <c r="D93" s="33"/>
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="34"/>
-      <c r="B94" s="34"/>
-      <c r="C94" s="62"/>
-      <c r="D94" s="34"/>
+      <c r="A94" s="33"/>
+      <c r="B94" s="33"/>
+      <c r="C94" s="56"/>
+      <c r="D94" s="33"/>
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="34"/>
-      <c r="B95" s="34"/>
-      <c r="C95" s="62"/>
-      <c r="D95" s="34"/>
+      <c r="A95" s="33"/>
+      <c r="B95" s="33"/>
+      <c r="C95" s="56"/>
+      <c r="D95" s="33"/>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="34"/>
-      <c r="B96" s="34"/>
-      <c r="C96" s="62"/>
-      <c r="D96" s="34"/>
+      <c r="A96" s="33"/>
+      <c r="B96" s="33"/>
+      <c r="C96" s="56"/>
+      <c r="D96" s="33"/>
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="34"/>
-      <c r="B97" s="34"/>
-      <c r="C97" s="62"/>
-      <c r="D97" s="34"/>
+      <c r="A97" s="33"/>
+      <c r="B97" s="33"/>
+      <c r="C97" s="56"/>
+      <c r="D97" s="33"/>
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="34"/>
-      <c r="B98" s="34"/>
-      <c r="C98" s="64"/>
-      <c r="D98" s="34"/>
+      <c r="A98" s="33"/>
+      <c r="B98" s="33"/>
+      <c r="C98" s="58"/>
+      <c r="D98" s="33"/>
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="34"/>
-      <c r="B99" s="34"/>
-      <c r="C99" s="62"/>
-      <c r="D99" s="34"/>
+      <c r="A99" s="33"/>
+      <c r="B99" s="33"/>
+      <c r="C99" s="56"/>
+      <c r="D99" s="33"/>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="34"/>
-      <c r="B100" s="34"/>
-      <c r="C100" s="62"/>
-      <c r="D100" s="34"/>
+      <c r="A100" s="33"/>
+      <c r="B100" s="33"/>
+      <c r="C100" s="56"/>
+      <c r="D100" s="33"/>
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="34"/>
-      <c r="B101" s="34"/>
-      <c r="C101" s="62"/>
-      <c r="D101" s="34"/>
+      <c r="A101" s="33"/>
+      <c r="B101" s="33"/>
+      <c r="C101" s="56"/>
+      <c r="D101" s="33"/>
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="34"/>
-      <c r="B102" s="34"/>
-      <c r="C102" s="62"/>
-      <c r="D102" s="34"/>
+      <c r="A102" s="33"/>
+      <c r="B102" s="33"/>
+      <c r="C102" s="56"/>
+      <c r="D102" s="33"/>
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="34"/>
-      <c r="B103" s="34"/>
-      <c r="C103" s="62"/>
-      <c r="D103" s="34"/>
+      <c r="A103" s="33"/>
+      <c r="B103" s="33"/>
+      <c r="C103" s="56"/>
+      <c r="D103" s="33"/>
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="34"/>
-      <c r="B104" s="34"/>
-      <c r="C104" s="62"/>
-      <c r="D104" s="34"/>
+      <c r="A104" s="33"/>
+      <c r="B104" s="33"/>
+      <c r="C104" s="56"/>
+      <c r="D104" s="33"/>
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="34"/>
-      <c r="B105" s="34"/>
-      <c r="C105" s="62"/>
-      <c r="D105" s="34"/>
+      <c r="A105" s="33"/>
+      <c r="B105" s="33"/>
+      <c r="C105" s="56"/>
+      <c r="D105" s="33"/>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="34"/>
-      <c r="B106" s="34"/>
-      <c r="C106" s="62"/>
-      <c r="D106" s="34"/>
+      <c r="A106" s="33"/>
+      <c r="B106" s="33"/>
+      <c r="C106" s="56"/>
+      <c r="D106" s="33"/>
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="34"/>
-      <c r="B107" s="34"/>
-      <c r="C107" s="62"/>
-      <c r="D107" s="34"/>
+      <c r="A107" s="33"/>
+      <c r="B107" s="33"/>
+      <c r="C107" s="56"/>
+      <c r="D107" s="33"/>
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="34"/>
-      <c r="B108" s="34"/>
-      <c r="C108" s="62"/>
-      <c r="D108" s="34"/>
+      <c r="A108" s="33"/>
+      <c r="B108" s="33"/>
+      <c r="C108" s="56"/>
+      <c r="D108" s="33"/>
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="34"/>
-      <c r="B109" s="34"/>
-      <c r="C109" s="62"/>
-      <c r="D109" s="34"/>
+      <c r="A109" s="33"/>
+      <c r="B109" s="33"/>
+      <c r="C109" s="56"/>
+      <c r="D109" s="33"/>
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="34"/>
-      <c r="B110" s="34"/>
-      <c r="C110" s="62"/>
-      <c r="D110" s="34"/>
+      <c r="A110" s="33"/>
+      <c r="B110" s="33"/>
+      <c r="C110" s="56"/>
+      <c r="D110" s="33"/>
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="34"/>
-      <c r="B111" s="34"/>
-      <c r="C111" s="62"/>
-      <c r="D111" s="34"/>
+      <c r="A111" s="33"/>
+      <c r="B111" s="33"/>
+      <c r="C111" s="56"/>
+      <c r="D111" s="33"/>
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="34"/>
-      <c r="B112" s="34"/>
-      <c r="C112" s="62"/>
-      <c r="D112" s="34"/>
+      <c r="A112" s="33"/>
+      <c r="B112" s="33"/>
+      <c r="C112" s="56"/>
+      <c r="D112" s="33"/>
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="34"/>
-      <c r="B113" s="34"/>
-      <c r="C113" s="62"/>
-      <c r="D113" s="34"/>
+      <c r="A113" s="33"/>
+      <c r="B113" s="33"/>
+      <c r="C113" s="56"/>
+      <c r="D113" s="33"/>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="34"/>
-      <c r="B114" s="34"/>
-      <c r="C114" s="62"/>
-      <c r="D114" s="34"/>
+      <c r="A114" s="33"/>
+      <c r="B114" s="33"/>
+      <c r="C114" s="56"/>
+      <c r="D114" s="33"/>
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="34"/>
-      <c r="B115" s="34"/>
-      <c r="C115" s="62"/>
-      <c r="D115" s="34"/>
+      <c r="A115" s="33"/>
+      <c r="B115" s="33"/>
+      <c r="C115" s="56"/>
+      <c r="D115" s="33"/>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="34"/>
-      <c r="B116" s="34"/>
-      <c r="C116" s="62"/>
-      <c r="D116" s="34"/>
+      <c r="A116" s="33"/>
+      <c r="B116" s="33"/>
+      <c r="C116" s="56"/>
+      <c r="D116" s="33"/>
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="34"/>
-      <c r="B117" s="34"/>
-      <c r="C117" s="62"/>
-      <c r="D117" s="34"/>
+      <c r="A117" s="33"/>
+      <c r="B117" s="33"/>
+      <c r="C117" s="56"/>
+      <c r="D117" s="33"/>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="34"/>
-      <c r="B118" s="34"/>
-      <c r="C118" s="62"/>
-      <c r="D118" s="34"/>
+      <c r="A118" s="33"/>
+      <c r="B118" s="33"/>
+      <c r="C118" s="56"/>
+      <c r="D118" s="33"/>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="34"/>
-      <c r="B119" s="34"/>
-      <c r="C119" s="62"/>
-      <c r="D119" s="34"/>
+      <c r="A119" s="33"/>
+      <c r="B119" s="33"/>
+      <c r="C119" s="56"/>
+      <c r="D119" s="33"/>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="34"/>
-      <c r="B120" s="34"/>
-      <c r="C120" s="62"/>
-      <c r="D120" s="34"/>
+      <c r="A120" s="33"/>
+      <c r="B120" s="33"/>
+      <c r="C120" s="56"/>
+      <c r="D120" s="33"/>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="34"/>
-      <c r="B121" s="34"/>
-      <c r="C121" s="62"/>
-      <c r="D121" s="34"/>
+      <c r="A121" s="33"/>
+      <c r="B121" s="33"/>
+      <c r="C121" s="56"/>
+      <c r="D121" s="33"/>
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="34"/>
-      <c r="B122" s="34"/>
-      <c r="C122" s="62"/>
-      <c r="D122" s="34"/>
+      <c r="A122" s="33"/>
+      <c r="B122" s="33"/>
+      <c r="C122" s="56"/>
+      <c r="D122" s="33"/>
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="34"/>
-      <c r="B123" s="34"/>
-      <c r="C123" s="62"/>
-      <c r="D123" s="34"/>
+      <c r="A123" s="33"/>
+      <c r="B123" s="33"/>
+      <c r="C123" s="56"/>
+      <c r="D123" s="33"/>
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="34"/>
-      <c r="B124" s="34"/>
-      <c r="C124" s="62"/>
-      <c r="D124" s="34"/>
+      <c r="A124" s="33"/>
+      <c r="B124" s="33"/>
+      <c r="C124" s="56"/>
+      <c r="D124" s="33"/>
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="34"/>
-      <c r="B125" s="34"/>
-      <c r="C125" s="62"/>
-      <c r="D125" s="34"/>
+      <c r="A125" s="33"/>
+      <c r="B125" s="33"/>
+      <c r="C125" s="56"/>
+      <c r="D125" s="33"/>
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="34"/>
-      <c r="B126" s="34"/>
-      <c r="C126" s="64"/>
-      <c r="D126" s="34"/>
+      <c r="A126" s="33"/>
+      <c r="B126" s="33"/>
+      <c r="C126" s="58"/>
+      <c r="D126" s="33"/>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="34"/>
-      <c r="B127" s="34"/>
-      <c r="C127" s="62"/>
-      <c r="D127" s="34"/>
+      <c r="A127" s="33"/>
+      <c r="B127" s="33"/>
+      <c r="C127" s="56"/>
+      <c r="D127" s="33"/>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="34"/>
-      <c r="B128" s="34"/>
-      <c r="C128" s="62"/>
-      <c r="D128" s="34"/>
+      <c r="A128" s="33"/>
+      <c r="B128" s="33"/>
+      <c r="C128" s="56"/>
+      <c r="D128" s="33"/>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="34"/>
-      <c r="B129" s="34"/>
-      <c r="C129" s="62"/>
-      <c r="D129" s="34"/>
+      <c r="A129" s="33"/>
+      <c r="B129" s="33"/>
+      <c r="C129" s="56"/>
+      <c r="D129" s="33"/>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="34"/>
-      <c r="B130" s="34"/>
-      <c r="C130" s="64"/>
-      <c r="D130" s="34"/>
+      <c r="A130" s="33"/>
+      <c r="B130" s="33"/>
+      <c r="C130" s="58"/>
+      <c r="D130" s="33"/>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="34"/>
-      <c r="B131" s="34"/>
-      <c r="C131" s="62"/>
-      <c r="D131" s="34"/>
+      <c r="A131" s="33"/>
+      <c r="B131" s="33"/>
+      <c r="C131" s="56"/>
+      <c r="D131" s="33"/>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="34"/>
-      <c r="B132" s="34"/>
-      <c r="C132" s="62"/>
-      <c r="D132" s="34"/>
+      <c r="A132" s="33"/>
+      <c r="B132" s="33"/>
+      <c r="C132" s="56"/>
+      <c r="D132" s="33"/>
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="34"/>
-      <c r="B133" s="34"/>
-      <c r="C133" s="62"/>
-      <c r="D133" s="34"/>
+      <c r="A133" s="33"/>
+      <c r="B133" s="33"/>
+      <c r="C133" s="56"/>
+      <c r="D133" s="33"/>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="34"/>
-      <c r="B134" s="34"/>
-      <c r="C134" s="62"/>
-      <c r="D134" s="34"/>
+      <c r="A134" s="33"/>
+      <c r="B134" s="33"/>
+      <c r="C134" s="56"/>
+      <c r="D134" s="33"/>
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="34"/>
-      <c r="B135" s="34"/>
-      <c r="C135" s="62"/>
-      <c r="D135" s="34"/>
+      <c r="A135" s="33"/>
+      <c r="B135" s="33"/>
+      <c r="C135" s="56"/>
+      <c r="D135" s="33"/>
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="34"/>
-      <c r="B136" s="34"/>
-      <c r="C136" s="62"/>
-      <c r="D136" s="34"/>
+      <c r="A136" s="33"/>
+      <c r="B136" s="33"/>
+      <c r="C136" s="56"/>
+      <c r="D136" s="33"/>
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="34"/>
-      <c r="B137" s="34"/>
-      <c r="C137" s="62"/>
-      <c r="D137" s="34"/>
+      <c r="A137" s="33"/>
+      <c r="B137" s="33"/>
+      <c r="C137" s="56"/>
+      <c r="D137" s="33"/>
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="34"/>
-      <c r="B138" s="34"/>
-      <c r="C138" s="62"/>
-      <c r="D138" s="34"/>
+      <c r="A138" s="33"/>
+      <c r="B138" s="33"/>
+      <c r="C138" s="56"/>
+      <c r="D138" s="33"/>
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="34"/>
-      <c r="B139" s="34"/>
-      <c r="C139" s="62"/>
-      <c r="D139" s="34"/>
+      <c r="A139" s="33"/>
+      <c r="B139" s="33"/>
+      <c r="C139" s="56"/>
+      <c r="D139" s="33"/>
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="34"/>
-      <c r="B140" s="34"/>
-      <c r="C140" s="62"/>
-      <c r="D140" s="34"/>
+      <c r="A140" s="33"/>
+      <c r="B140" s="33"/>
+      <c r="C140" s="56"/>
+      <c r="D140" s="33"/>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="34"/>
-      <c r="B141" s="34"/>
-      <c r="C141" s="62"/>
-      <c r="D141" s="34"/>
+      <c r="A141" s="33"/>
+      <c r="B141" s="33"/>
+      <c r="C141" s="56"/>
+      <c r="D141" s="33"/>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="34"/>
-      <c r="B142" s="34"/>
-      <c r="C142" s="62"/>
-      <c r="D142" s="34"/>
+      <c r="A142" s="33"/>
+      <c r="B142" s="33"/>
+      <c r="C142" s="56"/>
+      <c r="D142" s="33"/>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="34"/>
-      <c r="B143" s="34"/>
-      <c r="C143" s="62"/>
-      <c r="D143" s="34"/>
+      <c r="A143" s="33"/>
+      <c r="B143" s="33"/>
+      <c r="C143" s="56"/>
+      <c r="D143" s="33"/>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="34"/>
-      <c r="B144" s="34"/>
-      <c r="C144" s="62"/>
-      <c r="D144" s="34"/>
+      <c r="A144" s="33"/>
+      <c r="B144" s="33"/>
+      <c r="C144" s="56"/>
+      <c r="D144" s="33"/>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="34"/>
-      <c r="B145" s="34"/>
-      <c r="C145" s="62"/>
-      <c r="D145" s="34"/>
+      <c r="A145" s="33"/>
+      <c r="B145" s="33"/>
+      <c r="C145" s="56"/>
+      <c r="D145" s="33"/>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="34"/>
-      <c r="B146" s="34"/>
-      <c r="C146" s="62"/>
-      <c r="D146" s="34"/>
+      <c r="A146" s="33"/>
+      <c r="B146" s="33"/>
+      <c r="C146" s="56"/>
+      <c r="D146" s="33"/>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="34"/>
-      <c r="B147" s="34"/>
-      <c r="C147" s="62"/>
-      <c r="D147" s="34"/>
+      <c r="A147" s="33"/>
+      <c r="B147" s="33"/>
+      <c r="C147" s="56"/>
+      <c r="D147" s="33"/>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="34"/>
-      <c r="B148" s="34"/>
-      <c r="C148" s="62"/>
-      <c r="D148" s="34"/>
+      <c r="A148" s="33"/>
+      <c r="B148" s="33"/>
+      <c r="C148" s="56"/>
+      <c r="D148" s="33"/>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="34"/>
-      <c r="B149" s="34"/>
-      <c r="C149" s="62"/>
-      <c r="D149" s="34"/>
+      <c r="A149" s="33"/>
+      <c r="B149" s="33"/>
+      <c r="C149" s="56"/>
+      <c r="D149" s="33"/>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="34"/>
-      <c r="B150" s="34"/>
-      <c r="C150" s="62"/>
-      <c r="D150" s="34"/>
+      <c r="A150" s="33"/>
+      <c r="B150" s="33"/>
+      <c r="C150" s="56"/>
+      <c r="D150" s="33"/>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="34"/>
-      <c r="B151" s="34"/>
-      <c r="C151" s="62"/>
-      <c r="D151" s="34"/>
+      <c r="A151" s="33"/>
+      <c r="B151" s="33"/>
+      <c r="C151" s="56"/>
+      <c r="D151" s="33"/>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="34"/>
-      <c r="B152" s="34"/>
-      <c r="C152" s="62"/>
-      <c r="D152" s="34"/>
+      <c r="A152" s="33"/>
+      <c r="B152" s="33"/>
+      <c r="C152" s="56"/>
+      <c r="D152" s="33"/>
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="34"/>
-      <c r="B153" s="34"/>
-      <c r="C153" s="62"/>
-      <c r="D153" s="34"/>
+      <c r="A153" s="33"/>
+      <c r="B153" s="33"/>
+      <c r="C153" s="56"/>
+      <c r="D153" s="33"/>
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="34"/>
-      <c r="B154" s="34"/>
-      <c r="C154" s="62"/>
-      <c r="D154" s="34"/>
+      <c r="A154" s="33"/>
+      <c r="B154" s="33"/>
+      <c r="C154" s="56"/>
+      <c r="D154" s="33"/>
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="34"/>
-      <c r="B155" s="34"/>
-      <c r="C155" s="62"/>
-      <c r="D155" s="34"/>
+      <c r="A155" s="33"/>
+      <c r="B155" s="33"/>
+      <c r="C155" s="56"/>
+      <c r="D155" s="33"/>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="34"/>
-      <c r="B156" s="34"/>
-      <c r="C156" s="62"/>
-      <c r="D156" s="34"/>
+      <c r="A156" s="33"/>
+      <c r="B156" s="33"/>
+      <c r="C156" s="56"/>
+      <c r="D156" s="33"/>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="34"/>
-      <c r="B157" s="34"/>
-      <c r="C157" s="62"/>
-      <c r="D157" s="34"/>
+      <c r="A157" s="33"/>
+      <c r="B157" s="33"/>
+      <c r="C157" s="56"/>
+      <c r="D157" s="33"/>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="34"/>
-      <c r="B158" s="34"/>
-      <c r="C158" s="62"/>
-      <c r="D158" s="34"/>
+      <c r="A158" s="33"/>
+      <c r="B158" s="33"/>
+      <c r="C158" s="56"/>
+      <c r="D158" s="33"/>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="34"/>
-      <c r="B159" s="34"/>
-      <c r="C159" s="62"/>
-      <c r="D159" s="34"/>
+      <c r="A159" s="33"/>
+      <c r="B159" s="33"/>
+      <c r="C159" s="56"/>
+      <c r="D159" s="33"/>
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="34"/>
-      <c r="B160" s="34"/>
-      <c r="C160" s="62"/>
-      <c r="D160" s="34"/>
+      <c r="A160" s="33"/>
+      <c r="B160" s="33"/>
+      <c r="C160" s="56"/>
+      <c r="D160" s="33"/>
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="34"/>
-      <c r="B161" s="34"/>
-      <c r="C161" s="62"/>
-      <c r="D161" s="34"/>
+      <c r="A161" s="33"/>
+      <c r="B161" s="33"/>
+      <c r="C161" s="56"/>
+      <c r="D161" s="33"/>
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="34"/>
-      <c r="B162" s="34"/>
-      <c r="C162" s="62"/>
-      <c r="D162" s="34"/>
+      <c r="A162" s="33"/>
+      <c r="B162" s="33"/>
+      <c r="C162" s="56"/>
+      <c r="D162" s="33"/>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="34"/>
-      <c r="B163" s="34"/>
-      <c r="C163" s="62"/>
-      <c r="D163" s="34"/>
+      <c r="A163" s="33"/>
+      <c r="B163" s="33"/>
+      <c r="C163" s="56"/>
+      <c r="D163" s="33"/>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="34"/>
-      <c r="B164" s="34"/>
-      <c r="C164" s="62"/>
-      <c r="D164" s="34"/>
+      <c r="A164" s="33"/>
+      <c r="B164" s="33"/>
+      <c r="C164" s="56"/>
+      <c r="D164" s="33"/>
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="34"/>
-      <c r="B165" s="34"/>
-      <c r="C165" s="62"/>
-      <c r="D165" s="34"/>
+      <c r="A165" s="33"/>
+      <c r="B165" s="33"/>
+      <c r="C165" s="56"/>
+      <c r="D165" s="33"/>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="34"/>
-      <c r="B166" s="34"/>
-      <c r="C166" s="62"/>
-      <c r="D166" s="34"/>
+      <c r="A166" s="33"/>
+      <c r="B166" s="33"/>
+      <c r="C166" s="56"/>
+      <c r="D166" s="33"/>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="34"/>
-      <c r="B167" s="34"/>
-      <c r="C167" s="62"/>
-      <c r="D167" s="34"/>
+      <c r="A167" s="33"/>
+      <c r="B167" s="33"/>
+      <c r="C167" s="56"/>
+      <c r="D167" s="33"/>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="34"/>
-      <c r="B168" s="34"/>
-      <c r="C168" s="62"/>
-      <c r="D168" s="34"/>
+      <c r="A168" s="33"/>
+      <c r="B168" s="33"/>
+      <c r="C168" s="56"/>
+      <c r="D168" s="33"/>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="34"/>
-      <c r="B169" s="34"/>
-      <c r="C169" s="62"/>
-      <c r="D169" s="34"/>
+      <c r="A169" s="33"/>
+      <c r="B169" s="33"/>
+      <c r="C169" s="56"/>
+      <c r="D169" s="33"/>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="34"/>
-      <c r="B170" s="34"/>
-      <c r="C170" s="62"/>
-      <c r="D170" s="34"/>
+      <c r="A170" s="33"/>
+      <c r="B170" s="33"/>
+      <c r="C170" s="56"/>
+      <c r="D170" s="33"/>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="34"/>
-      <c r="B171" s="34"/>
-      <c r="C171" s="62"/>
-      <c r="D171" s="34"/>
+      <c r="A171" s="33"/>
+      <c r="B171" s="33"/>
+      <c r="C171" s="56"/>
+      <c r="D171" s="33"/>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="34"/>
-      <c r="B172" s="34"/>
-      <c r="C172" s="62"/>
-      <c r="D172" s="34"/>
+      <c r="A172" s="33"/>
+      <c r="B172" s="33"/>
+      <c r="C172" s="56"/>
+      <c r="D172" s="33"/>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="34"/>
-      <c r="B173" s="34"/>
-      <c r="C173" s="62"/>
-      <c r="D173" s="34"/>
+      <c r="A173" s="33"/>
+      <c r="B173" s="33"/>
+      <c r="C173" s="56"/>
+      <c r="D173" s="33"/>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="34"/>
-      <c r="B174" s="34"/>
-      <c r="C174" s="62"/>
-      <c r="D174" s="34"/>
+      <c r="A174" s="33"/>
+      <c r="B174" s="33"/>
+      <c r="C174" s="56"/>
+      <c r="D174" s="33"/>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A175" s="34"/>
-      <c r="B175" s="34"/>
-      <c r="C175" s="62"/>
-      <c r="D175" s="34"/>
+      <c r="A175" s="33"/>
+      <c r="B175" s="33"/>
+      <c r="C175" s="56"/>
+      <c r="D175" s="33"/>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="34"/>
-      <c r="B176" s="34"/>
-      <c r="C176" s="62"/>
-      <c r="D176" s="34"/>
+      <c r="A176" s="33"/>
+      <c r="B176" s="33"/>
+      <c r="C176" s="56"/>
+      <c r="D176" s="33"/>
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="34"/>
-      <c r="B177" s="34"/>
-      <c r="C177" s="62"/>
-      <c r="D177" s="34"/>
+      <c r="A177" s="33"/>
+      <c r="B177" s="33"/>
+      <c r="C177" s="56"/>
+      <c r="D177" s="33"/>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="34"/>
-      <c r="B178" s="34"/>
-      <c r="C178" s="62"/>
-      <c r="D178" s="34"/>
+      <c r="A178" s="33"/>
+      <c r="B178" s="33"/>
+      <c r="C178" s="56"/>
+      <c r="D178" s="33"/>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A179" s="34"/>
-      <c r="B179" s="34"/>
-      <c r="C179" s="62"/>
-      <c r="D179" s="34"/>
+      <c r="A179" s="33"/>
+      <c r="B179" s="33"/>
+      <c r="C179" s="56"/>
+      <c r="D179" s="33"/>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="34"/>
-      <c r="B180" s="34"/>
-      <c r="C180" s="62"/>
-      <c r="D180" s="34"/>
+      <c r="A180" s="33"/>
+      <c r="B180" s="33"/>
+      <c r="C180" s="56"/>
+      <c r="D180" s="33"/>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="34"/>
-      <c r="B181" s="34"/>
-      <c r="C181" s="62"/>
-      <c r="D181" s="34"/>
+      <c r="A181" s="33"/>
+      <c r="B181" s="33"/>
+      <c r="C181" s="56"/>
+      <c r="D181" s="33"/>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A182" s="34"/>
-      <c r="B182" s="34"/>
-      <c r="C182" s="62"/>
-      <c r="D182" s="34"/>
+      <c r="A182" s="33"/>
+      <c r="B182" s="33"/>
+      <c r="C182" s="56"/>
+      <c r="D182" s="33"/>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A183" s="34"/>
-      <c r="B183" s="34"/>
-      <c r="C183" s="62"/>
-      <c r="D183" s="34"/>
+      <c r="A183" s="33"/>
+      <c r="B183" s="33"/>
+      <c r="C183" s="56"/>
+      <c r="D183" s="33"/>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="34"/>
-      <c r="B184" s="34"/>
-      <c r="C184" s="62"/>
-      <c r="D184" s="34"/>
+      <c r="A184" s="33"/>
+      <c r="B184" s="33"/>
+      <c r="C184" s="56"/>
+      <c r="D184" s="33"/>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="34"/>
-      <c r="B185" s="34"/>
-      <c r="C185" s="62"/>
-      <c r="D185" s="34"/>
+      <c r="A185" s="33"/>
+      <c r="B185" s="33"/>
+      <c r="C185" s="56"/>
+      <c r="D185" s="33"/>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="34"/>
-      <c r="B186" s="34"/>
-      <c r="C186" s="62"/>
-      <c r="D186" s="34"/>
+      <c r="A186" s="33"/>
+      <c r="B186" s="33"/>
+      <c r="C186" s="56"/>
+      <c r="D186" s="33"/>
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="34"/>
-      <c r="B187" s="34"/>
-      <c r="C187" s="62"/>
-      <c r="D187" s="34"/>
+      <c r="A187" s="33"/>
+      <c r="B187" s="33"/>
+      <c r="C187" s="56"/>
+      <c r="D187" s="33"/>
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="34"/>
-      <c r="B188" s="34"/>
-      <c r="C188" s="62"/>
-      <c r="D188" s="34"/>
+      <c r="A188" s="33"/>
+      <c r="B188" s="33"/>
+      <c r="C188" s="56"/>
+      <c r="D188" s="33"/>
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A189" s="34"/>
-      <c r="B189" s="34"/>
-      <c r="C189" s="62"/>
-      <c r="D189" s="34"/>
+      <c r="A189" s="33"/>
+      <c r="B189" s="33"/>
+      <c r="C189" s="56"/>
+      <c r="D189" s="33"/>
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A190" s="34"/>
-      <c r="B190" s="34"/>
-      <c r="C190" s="62"/>
-      <c r="D190" s="34"/>
+      <c r="A190" s="33"/>
+      <c r="B190" s="33"/>
+      <c r="C190" s="56"/>
+      <c r="D190" s="33"/>
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="34"/>
-      <c r="B191" s="34"/>
-      <c r="C191" s="62"/>
-      <c r="D191" s="34"/>
+      <c r="A191" s="33"/>
+      <c r="B191" s="33"/>
+      <c r="C191" s="56"/>
+      <c r="D191" s="33"/>
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="34"/>
-      <c r="B192" s="34"/>
-      <c r="C192" s="62"/>
-      <c r="D192" s="34"/>
+      <c r="A192" s="33"/>
+      <c r="B192" s="33"/>
+      <c r="C192" s="56"/>
+      <c r="D192" s="33"/>
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A193" s="34"/>
-      <c r="B193" s="34"/>
-      <c r="C193" s="62"/>
-      <c r="D193" s="34"/>
+      <c r="A193" s="33"/>
+      <c r="B193" s="33"/>
+      <c r="C193" s="56"/>
+      <c r="D193" s="33"/>
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A194" s="34"/>
-      <c r="B194" s="34"/>
-      <c r="C194" s="62"/>
-      <c r="D194" s="34"/>
+      <c r="A194" s="33"/>
+      <c r="B194" s="33"/>
+      <c r="C194" s="56"/>
+      <c r="D194" s="33"/>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A195" s="34"/>
-      <c r="B195" s="34"/>
-      <c r="C195" s="62"/>
-      <c r="D195" s="34"/>
+      <c r="A195" s="33"/>
+      <c r="B195" s="33"/>
+      <c r="C195" s="56"/>
+      <c r="D195" s="33"/>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A196" s="34"/>
-      <c r="B196" s="34"/>
-      <c r="C196" s="62"/>
-      <c r="D196" s="34"/>
+      <c r="A196" s="33"/>
+      <c r="B196" s="33"/>
+      <c r="C196" s="56"/>
+      <c r="D196" s="33"/>
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A197" s="34"/>
-      <c r="B197" s="34"/>
-      <c r="C197" s="62"/>
-      <c r="D197" s="34"/>
+      <c r="A197" s="33"/>
+      <c r="B197" s="33"/>
+      <c r="C197" s="56"/>
+      <c r="D197" s="33"/>
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="34"/>
-      <c r="B198" s="34"/>
-      <c r="C198" s="62"/>
-      <c r="D198" s="34"/>
+      <c r="A198" s="33"/>
+      <c r="B198" s="33"/>
+      <c r="C198" s="56"/>
+      <c r="D198" s="33"/>
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="34"/>
-      <c r="B199" s="34"/>
-      <c r="C199" s="62"/>
-      <c r="D199" s="34"/>
+      <c r="A199" s="33"/>
+      <c r="B199" s="33"/>
+      <c r="C199" s="56"/>
+      <c r="D199" s="33"/>
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="34"/>
-      <c r="B200" s="34"/>
-      <c r="C200" s="62"/>
-      <c r="D200" s="34"/>
+      <c r="A200" s="33"/>
+      <c r="B200" s="33"/>
+      <c r="C200" s="56"/>
+      <c r="D200" s="33"/>
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A201" s="34"/>
-      <c r="B201" s="34"/>
-      <c r="C201" s="62"/>
-      <c r="D201" s="34"/>
+      <c r="A201" s="33"/>
+      <c r="B201" s="33"/>
+      <c r="C201" s="56"/>
+      <c r="D201" s="33"/>
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="34"/>
-      <c r="B202" s="34"/>
-      <c r="C202" s="62"/>
-      <c r="D202" s="34"/>
+      <c r="A202" s="33"/>
+      <c r="B202" s="33"/>
+      <c r="C202" s="56"/>
+      <c r="D202" s="33"/>
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="34"/>
-      <c r="B203" s="34"/>
-      <c r="C203" s="62"/>
-      <c r="D203" s="34"/>
+      <c r="A203" s="33"/>
+      <c r="B203" s="33"/>
+      <c r="C203" s="56"/>
+      <c r="D203" s="33"/>
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="34"/>
-      <c r="B204" s="34"/>
-      <c r="C204" s="64"/>
-      <c r="D204" s="34"/>
+      <c r="A204" s="33"/>
+      <c r="B204" s="33"/>
+      <c r="C204" s="58"/>
+      <c r="D204" s="33"/>
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A205" s="34"/>
-      <c r="B205" s="34"/>
-      <c r="C205" s="62"/>
-      <c r="D205" s="34"/>
+      <c r="A205" s="33"/>
+      <c r="B205" s="33"/>
+      <c r="C205" s="56"/>
+      <c r="D205" s="33"/>
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A206" s="34"/>
-      <c r="B206" s="34"/>
-      <c r="C206" s="62"/>
-      <c r="D206" s="34"/>
+      <c r="A206" s="33"/>
+      <c r="B206" s="33"/>
+      <c r="C206" s="56"/>
+      <c r="D206" s="33"/>
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A207" s="34"/>
-      <c r="B207" s="34"/>
-      <c r="C207" s="62"/>
-      <c r="D207" s="34"/>
+      <c r="A207" s="33"/>
+      <c r="B207" s="33"/>
+      <c r="C207" s="56"/>
+      <c r="D207" s="33"/>
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="34"/>
-      <c r="B208" s="34"/>
-      <c r="C208" s="62"/>
-      <c r="D208" s="34"/>
+      <c r="A208" s="33"/>
+      <c r="B208" s="33"/>
+      <c r="C208" s="56"/>
+      <c r="D208" s="33"/>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="34"/>
-      <c r="B209" s="34"/>
-      <c r="C209" s="62"/>
-      <c r="D209" s="34"/>
+      <c r="A209" s="33"/>
+      <c r="B209" s="33"/>
+      <c r="C209" s="56"/>
+      <c r="D209" s="33"/>
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="34"/>
-      <c r="B210" s="34"/>
-      <c r="C210" s="62"/>
-      <c r="D210" s="34"/>
+      <c r="A210" s="33"/>
+      <c r="B210" s="33"/>
+      <c r="C210" s="56"/>
+      <c r="D210" s="33"/>
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="34"/>
-      <c r="B211" s="34"/>
-      <c r="C211" s="62"/>
-      <c r="D211" s="34"/>
+      <c r="A211" s="33"/>
+      <c r="B211" s="33"/>
+      <c r="C211" s="56"/>
+      <c r="D211" s="33"/>
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A212" s="34"/>
-      <c r="B212" s="34"/>
-      <c r="C212" s="62"/>
-      <c r="D212" s="34"/>
+      <c r="A212" s="33"/>
+      <c r="B212" s="33"/>
+      <c r="C212" s="56"/>
+      <c r="D212" s="33"/>
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A213" s="34"/>
-      <c r="B213" s="34"/>
-      <c r="C213" s="62"/>
-      <c r="D213" s="34"/>
+      <c r="A213" s="33"/>
+      <c r="B213" s="33"/>
+      <c r="C213" s="56"/>
+      <c r="D213" s="33"/>
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A214" s="34"/>
-      <c r="B214" s="34"/>
-      <c r="C214" s="62"/>
-      <c r="D214" s="34"/>
+      <c r="A214" s="33"/>
+      <c r="B214" s="33"/>
+      <c r="C214" s="56"/>
+      <c r="D214" s="33"/>
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A215" s="34"/>
-      <c r="B215" s="34"/>
-      <c r="C215" s="62"/>
-      <c r="D215" s="34"/>
+      <c r="A215" s="33"/>
+      <c r="B215" s="33"/>
+      <c r="C215" s="56"/>
+      <c r="D215" s="33"/>
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A216" s="34"/>
-      <c r="B216" s="34"/>
-      <c r="C216" s="62"/>
-      <c r="D216" s="34"/>
+      <c r="A216" s="33"/>
+      <c r="B216" s="33"/>
+      <c r="C216" s="56"/>
+      <c r="D216" s="33"/>
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A217" s="34"/>
-      <c r="B217" s="34"/>
-      <c r="C217" s="62"/>
-      <c r="D217" s="34"/>
+      <c r="A217" s="33"/>
+      <c r="B217" s="33"/>
+      <c r="C217" s="56"/>
+      <c r="D217" s="33"/>
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A218" s="34"/>
-      <c r="B218" s="34"/>
-      <c r="C218" s="62"/>
-      <c r="D218" s="34"/>
+      <c r="A218" s="33"/>
+      <c r="B218" s="33"/>
+      <c r="C218" s="56"/>
+      <c r="D218" s="33"/>
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A219" s="34"/>
-      <c r="B219" s="34"/>
-      <c r="C219" s="62"/>
-      <c r="D219" s="34"/>
+      <c r="A219" s="33"/>
+      <c r="B219" s="33"/>
+      <c r="C219" s="56"/>
+      <c r="D219" s="33"/>
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A220" s="34"/>
-      <c r="B220" s="34"/>
-      <c r="C220" s="62"/>
-      <c r="D220" s="34"/>
+      <c r="A220" s="33"/>
+      <c r="B220" s="33"/>
+      <c r="C220" s="56"/>
+      <c r="D220" s="33"/>
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A221" s="34"/>
-      <c r="B221" s="34"/>
-      <c r="C221" s="62"/>
-      <c r="D221" s="34"/>
+      <c r="A221" s="33"/>
+      <c r="B221" s="33"/>
+      <c r="C221" s="56"/>
+      <c r="D221" s="33"/>
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A222" s="34"/>
-      <c r="B222" s="34"/>
-      <c r="C222" s="62"/>
-      <c r="D222" s="34"/>
+      <c r="A222" s="33"/>
+      <c r="B222" s="33"/>
+      <c r="C222" s="56"/>
+      <c r="D222" s="33"/>
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A223" s="34"/>
-      <c r="B223" s="34"/>
-      <c r="C223" s="62"/>
-      <c r="D223" s="34"/>
+      <c r="A223" s="33"/>
+      <c r="B223" s="33"/>
+      <c r="C223" s="56"/>
+      <c r="D223" s="33"/>
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A224" s="34"/>
-      <c r="B224" s="34"/>
-      <c r="C224" s="62"/>
-      <c r="D224" s="34"/>
+      <c r="A224" s="33"/>
+      <c r="B224" s="33"/>
+      <c r="C224" s="56"/>
+      <c r="D224" s="33"/>
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A225" s="34"/>
-      <c r="B225" s="34"/>
-      <c r="C225" s="62"/>
-      <c r="D225" s="34"/>
+      <c r="A225" s="33"/>
+      <c r="B225" s="33"/>
+      <c r="C225" s="56"/>
+      <c r="D225" s="33"/>
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A226" s="34"/>
-      <c r="B226" s="34"/>
-      <c r="C226" s="62"/>
-      <c r="D226" s="34"/>
+      <c r="A226" s="33"/>
+      <c r="B226" s="33"/>
+      <c r="C226" s="56"/>
+      <c r="D226" s="33"/>
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A227" s="34"/>
-      <c r="B227" s="34"/>
-      <c r="C227" s="62"/>
-      <c r="D227" s="34"/>
+      <c r="A227" s="33"/>
+      <c r="B227" s="33"/>
+      <c r="C227" s="56"/>
+      <c r="D227" s="33"/>
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A228" s="34"/>
-      <c r="B228" s="34"/>
-      <c r="C228" s="62"/>
-      <c r="D228" s="34"/>
+      <c r="A228" s="33"/>
+      <c r="B228" s="33"/>
+      <c r="C228" s="56"/>
+      <c r="D228" s="33"/>
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A229" s="34"/>
-      <c r="B229" s="34"/>
-      <c r="C229" s="62"/>
-      <c r="D229" s="34"/>
+      <c r="A229" s="33"/>
+      <c r="B229" s="33"/>
+      <c r="C229" s="56"/>
+      <c r="D229" s="33"/>
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A230" s="34"/>
-      <c r="B230" s="34"/>
-      <c r="C230" s="62"/>
-      <c r="D230" s="34"/>
+      <c r="A230" s="33"/>
+      <c r="B230" s="33"/>
+      <c r="C230" s="56"/>
+      <c r="D230" s="33"/>
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A231" s="34"/>
-      <c r="B231" s="34"/>
-      <c r="C231" s="62"/>
-      <c r="D231" s="34"/>
+      <c r="A231" s="33"/>
+      <c r="B231" s="33"/>
+      <c r="C231" s="56"/>
+      <c r="D231" s="33"/>
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A232" s="34"/>
-      <c r="B232" s="34"/>
-      <c r="C232" s="62"/>
-      <c r="D232" s="34"/>
+      <c r="A232" s="33"/>
+      <c r="B232" s="33"/>
+      <c r="C232" s="56"/>
+      <c r="D232" s="33"/>
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A233" s="34"/>
-      <c r="B233" s="34"/>
-      <c r="C233" s="62"/>
-      <c r="D233" s="34"/>
+      <c r="A233" s="33"/>
+      <c r="B233" s="33"/>
+      <c r="C233" s="56"/>
+      <c r="D233" s="33"/>
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A234" s="34"/>
-      <c r="B234" s="34"/>
-      <c r="C234" s="62"/>
-      <c r="D234" s="34"/>
+      <c r="A234" s="33"/>
+      <c r="B234" s="33"/>
+      <c r="C234" s="56"/>
+      <c r="D234" s="33"/>
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A235" s="34"/>
-      <c r="B235" s="34"/>
-      <c r="C235" s="62"/>
-      <c r="D235" s="34"/>
+      <c r="A235" s="33"/>
+      <c r="B235" s="33"/>
+      <c r="C235" s="56"/>
+      <c r="D235" s="33"/>
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A236" s="34"/>
-      <c r="B236" s="34"/>
-      <c r="C236" s="62"/>
-      <c r="D236" s="34"/>
+      <c r="A236" s="33"/>
+      <c r="B236" s="33"/>
+      <c r="C236" s="56"/>
+      <c r="D236" s="33"/>
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A237" s="34"/>
-      <c r="B237" s="34"/>
-      <c r="C237" s="62"/>
-      <c r="D237" s="34"/>
+      <c r="A237" s="33"/>
+      <c r="B237" s="33"/>
+      <c r="C237" s="56"/>
+      <c r="D237" s="33"/>
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A238" s="34"/>
-      <c r="B238" s="34"/>
-      <c r="C238" s="62"/>
-      <c r="D238" s="34"/>
+      <c r="A238" s="33"/>
+      <c r="B238" s="33"/>
+      <c r="C238" s="56"/>
+      <c r="D238" s="33"/>
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A239" s="34"/>
-      <c r="B239" s="34"/>
-      <c r="C239" s="62"/>
-      <c r="D239" s="34"/>
+      <c r="A239" s="33"/>
+      <c r="B239" s="33"/>
+      <c r="C239" s="56"/>
+      <c r="D239" s="33"/>
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A240" s="34"/>
-      <c r="B240" s="34"/>
-      <c r="C240" s="62"/>
-      <c r="D240" s="34"/>
+      <c r="A240" s="33"/>
+      <c r="B240" s="33"/>
+      <c r="C240" s="56"/>
+      <c r="D240" s="33"/>
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A241" s="34"/>
-      <c r="B241" s="34"/>
-      <c r="C241" s="62"/>
-      <c r="D241" s="34"/>
+      <c r="A241" s="33"/>
+      <c r="B241" s="33"/>
+      <c r="C241" s="56"/>
+      <c r="D241" s="33"/>
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A242" s="34"/>
-      <c r="B242" s="34"/>
-      <c r="C242" s="62"/>
-      <c r="D242" s="34"/>
+      <c r="A242" s="33"/>
+      <c r="B242" s="33"/>
+      <c r="C242" s="56"/>
+      <c r="D242" s="33"/>
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A243" s="34"/>
-      <c r="B243" s="34"/>
-      <c r="C243" s="62"/>
-      <c r="D243" s="34"/>
+      <c r="A243" s="33"/>
+      <c r="B243" s="33"/>
+      <c r="C243" s="56"/>
+      <c r="D243" s="33"/>
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A244" s="34"/>
-      <c r="B244" s="34"/>
-      <c r="C244" s="62"/>
-      <c r="D244" s="34"/>
+      <c r="A244" s="33"/>
+      <c r="B244" s="33"/>
+      <c r="C244" s="56"/>
+      <c r="D244" s="33"/>
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A245" s="34"/>
-      <c r="B245" s="34"/>
-      <c r="C245" s="62"/>
-      <c r="D245" s="34"/>
+      <c r="A245" s="33"/>
+      <c r="B245" s="33"/>
+      <c r="C245" s="56"/>
+      <c r="D245" s="33"/>
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A246" s="34"/>
-      <c r="B246" s="34"/>
-      <c r="C246" s="62"/>
-      <c r="D246" s="34"/>
+      <c r="A246" s="33"/>
+      <c r="B246" s="33"/>
+      <c r="C246" s="56"/>
+      <c r="D246" s="33"/>
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A247" s="34"/>
-      <c r="B247" s="34"/>
-      <c r="C247" s="62"/>
-      <c r="D247" s="34"/>
+      <c r="A247" s="33"/>
+      <c r="B247" s="33"/>
+      <c r="C247" s="56"/>
+      <c r="D247" s="33"/>
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A248" s="34"/>
-      <c r="B248" s="34"/>
-      <c r="C248" s="62"/>
-      <c r="D248" s="34"/>
+      <c r="A248" s="33"/>
+      <c r="B248" s="33"/>
+      <c r="C248" s="56"/>
+      <c r="D248" s="33"/>
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A249" s="34"/>
-      <c r="B249" s="34"/>
-      <c r="C249" s="62"/>
-      <c r="D249" s="34"/>
+      <c r="A249" s="33"/>
+      <c r="B249" s="33"/>
+      <c r="C249" s="56"/>
+      <c r="D249" s="33"/>
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A250" s="34"/>
-      <c r="B250" s="34"/>
-      <c r="C250" s="62"/>
-      <c r="D250" s="34"/>
+      <c r="A250" s="33"/>
+      <c r="B250" s="33"/>
+      <c r="C250" s="56"/>
+      <c r="D250" s="33"/>
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A251" s="34"/>
-      <c r="B251" s="34"/>
-      <c r="C251" s="62"/>
-      <c r="D251" s="34"/>
+      <c r="A251" s="33"/>
+      <c r="B251" s="33"/>
+      <c r="C251" s="56"/>
+      <c r="D251" s="33"/>
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A252" s="34"/>
-      <c r="B252" s="34"/>
-      <c r="C252" s="62"/>
-      <c r="D252" s="34"/>
+      <c r="A252" s="33"/>
+      <c r="B252" s="33"/>
+      <c r="C252" s="56"/>
+      <c r="D252" s="33"/>
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A253" s="34"/>
-      <c r="B253" s="34"/>
-      <c r="C253" s="62"/>
-      <c r="D253" s="34"/>
+      <c r="A253" s="33"/>
+      <c r="B253" s="33"/>
+      <c r="C253" s="56"/>
+      <c r="D253" s="33"/>
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A254" s="34"/>
-      <c r="B254" s="34"/>
-      <c r="C254" s="62"/>
-      <c r="D254" s="34"/>
+      <c r="A254" s="33"/>
+      <c r="B254" s="33"/>
+      <c r="C254" s="56"/>
+      <c r="D254" s="33"/>
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A255" s="34"/>
-      <c r="B255" s="34"/>
-      <c r="C255" s="62"/>
-      <c r="D255" s="34"/>
+      <c r="A255" s="33"/>
+      <c r="B255" s="33"/>
+      <c r="C255" s="56"/>
+      <c r="D255" s="33"/>
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A256" s="34"/>
-      <c r="B256" s="34"/>
-      <c r="C256" s="62"/>
-      <c r="D256" s="34"/>
+      <c r="A256" s="33"/>
+      <c r="B256" s="33"/>
+      <c r="C256" s="56"/>
+      <c r="D256" s="33"/>
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A257" s="34"/>
-      <c r="B257" s="34"/>
-      <c r="C257" s="62"/>
-      <c r="D257" s="34"/>
+      <c r="A257" s="33"/>
+      <c r="B257" s="33"/>
+      <c r="C257" s="56"/>
+      <c r="D257" s="33"/>
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A258" s="34"/>
-      <c r="B258" s="34"/>
-      <c r="C258" s="62"/>
-      <c r="D258" s="34"/>
+      <c r="A258" s="33"/>
+      <c r="B258" s="33"/>
+      <c r="C258" s="56"/>
+      <c r="D258" s="33"/>
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A259" s="34"/>
-      <c r="B259" s="34"/>
-      <c r="C259" s="62"/>
-      <c r="D259" s="34"/>
+      <c r="A259" s="33"/>
+      <c r="B259" s="33"/>
+      <c r="C259" s="56"/>
+      <c r="D259" s="33"/>
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A260" s="34"/>
-      <c r="B260" s="34"/>
-      <c r="C260" s="62"/>
-      <c r="D260" s="34"/>
+      <c r="A260" s="33"/>
+      <c r="B260" s="33"/>
+      <c r="C260" s="56"/>
+      <c r="D260" s="33"/>
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A261" s="34"/>
-      <c r="B261" s="34"/>
-      <c r="C261" s="62"/>
-      <c r="D261" s="34"/>
+      <c r="A261" s="33"/>
+      <c r="B261" s="33"/>
+      <c r="C261" s="56"/>
+      <c r="D261" s="33"/>
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A262" s="34"/>
-      <c r="B262" s="34"/>
-      <c r="C262" s="62"/>
-      <c r="D262" s="34"/>
+      <c r="A262" s="33"/>
+      <c r="B262" s="33"/>
+      <c r="C262" s="56"/>
+      <c r="D262" s="33"/>
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A263" s="34"/>
-      <c r="B263" s="34"/>
-      <c r="C263" s="62"/>
-      <c r="D263" s="34"/>
+      <c r="A263" s="33"/>
+      <c r="B263" s="33"/>
+      <c r="C263" s="56"/>
+      <c r="D263" s="33"/>
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A264" s="34"/>
-      <c r="B264" s="34"/>
-      <c r="C264" s="62"/>
-      <c r="D264" s="34"/>
+      <c r="A264" s="33"/>
+      <c r="B264" s="33"/>
+      <c r="C264" s="56"/>
+      <c r="D264" s="33"/>
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A265" s="34"/>
-      <c r="B265" s="34"/>
-      <c r="C265" s="62"/>
-      <c r="D265" s="34"/>
+      <c r="A265" s="33"/>
+      <c r="B265" s="33"/>
+      <c r="C265" s="56"/>
+      <c r="D265" s="33"/>
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A266" s="34"/>
-      <c r="B266" s="34"/>
-      <c r="C266" s="62"/>
-      <c r="D266" s="34"/>
+      <c r="A266" s="33"/>
+      <c r="B266" s="33"/>
+      <c r="C266" s="56"/>
+      <c r="D266" s="33"/>
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A267" s="34"/>
-      <c r="B267" s="34"/>
-      <c r="C267" s="62"/>
-      <c r="D267" s="34"/>
+      <c r="A267" s="33"/>
+      <c r="B267" s="33"/>
+      <c r="C267" s="56"/>
+      <c r="D267" s="33"/>
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A268" s="34"/>
-      <c r="B268" s="34"/>
-      <c r="C268" s="64"/>
-      <c r="D268" s="34"/>
+      <c r="A268" s="33"/>
+      <c r="B268" s="33"/>
+      <c r="C268" s="58"/>
+      <c r="D268" s="33"/>
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A269" s="34"/>
-      <c r="B269" s="34"/>
-      <c r="C269" s="62"/>
-      <c r="D269" s="34"/>
+      <c r="A269" s="33"/>
+      <c r="B269" s="33"/>
+      <c r="C269" s="56"/>
+      <c r="D269" s="33"/>
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A270" s="34"/>
-      <c r="B270" s="34"/>
-      <c r="C270" s="62"/>
-      <c r="D270" s="34"/>
+      <c r="A270" s="33"/>
+      <c r="B270" s="33"/>
+      <c r="C270" s="56"/>
+      <c r="D270" s="33"/>
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A271" s="34"/>
-      <c r="B271" s="34"/>
-      <c r="C271" s="62"/>
-      <c r="D271" s="34"/>
+      <c r="A271" s="33"/>
+      <c r="B271" s="33"/>
+      <c r="C271" s="56"/>
+      <c r="D271" s="33"/>
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A272" s="34"/>
-      <c r="B272" s="34"/>
-      <c r="C272" s="62"/>
-      <c r="D272" s="34"/>
+      <c r="A272" s="33"/>
+      <c r="B272" s="33"/>
+      <c r="C272" s="56"/>
+      <c r="D272" s="33"/>
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A273" s="34"/>
-      <c r="B273" s="34"/>
-      <c r="C273" s="62"/>
-      <c r="D273" s="34"/>
+      <c r="A273" s="33"/>
+      <c r="B273" s="33"/>
+      <c r="C273" s="56"/>
+      <c r="D273" s="33"/>
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A274" s="34"/>
-      <c r="B274" s="34"/>
-      <c r="C274" s="62"/>
-      <c r="D274" s="34"/>
+      <c r="A274" s="33"/>
+      <c r="B274" s="33"/>
+      <c r="C274" s="56"/>
+      <c r="D274" s="33"/>
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A275" s="34"/>
-      <c r="B275" s="34"/>
-      <c r="C275" s="62"/>
-      <c r="D275" s="34"/>
+      <c r="A275" s="33"/>
+      <c r="B275" s="33"/>
+      <c r="C275" s="56"/>
+      <c r="D275" s="33"/>
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A276" s="34"/>
-      <c r="B276" s="34"/>
-      <c r="C276" s="62"/>
-      <c r="D276" s="34"/>
+      <c r="A276" s="33"/>
+      <c r="B276" s="33"/>
+      <c r="C276" s="56"/>
+      <c r="D276" s="33"/>
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A277" s="34"/>
-      <c r="B277" s="34"/>
-      <c r="C277" s="62"/>
-      <c r="D277" s="34"/>
+      <c r="A277" s="33"/>
+      <c r="B277" s="33"/>
+      <c r="C277" s="56"/>
+      <c r="D277" s="33"/>
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A278" s="34"/>
-      <c r="B278" s="34"/>
-      <c r="C278" s="62"/>
-      <c r="D278" s="34"/>
+      <c r="A278" s="33"/>
+      <c r="B278" s="33"/>
+      <c r="C278" s="56"/>
+      <c r="D278" s="33"/>
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A279" s="34"/>
-      <c r="B279" s="34"/>
-      <c r="C279" s="62"/>
-      <c r="D279" s="34"/>
+      <c r="A279" s="33"/>
+      <c r="B279" s="33"/>
+      <c r="C279" s="56"/>
+      <c r="D279" s="33"/>
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A280" s="34"/>
-      <c r="B280" s="34"/>
-      <c r="C280" s="62"/>
-      <c r="D280" s="34"/>
+      <c r="A280" s="33"/>
+      <c r="B280" s="33"/>
+      <c r="C280" s="56"/>
+      <c r="D280" s="33"/>
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A281" s="34"/>
-      <c r="B281" s="34"/>
-      <c r="C281" s="62"/>
-      <c r="D281" s="34"/>
+      <c r="A281" s="33"/>
+      <c r="B281" s="33"/>
+      <c r="C281" s="56"/>
+      <c r="D281" s="33"/>
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A282" s="34"/>
-      <c r="B282" s="34"/>
-      <c r="C282" s="62"/>
-      <c r="D282" s="34"/>
+      <c r="A282" s="33"/>
+      <c r="B282" s="33"/>
+      <c r="C282" s="56"/>
+      <c r="D282" s="33"/>
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A283" s="34"/>
-      <c r="B283" s="34"/>
-      <c r="C283" s="62"/>
-      <c r="D283" s="34"/>
+      <c r="A283" s="33"/>
+      <c r="B283" s="33"/>
+      <c r="C283" s="56"/>
+      <c r="D283" s="33"/>
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A284" s="34"/>
-      <c r="B284" s="34"/>
-      <c r="C284" s="62"/>
-      <c r="D284" s="34"/>
+      <c r="A284" s="33"/>
+      <c r="B284" s="33"/>
+      <c r="C284" s="56"/>
+      <c r="D284" s="33"/>
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A285" s="34"/>
-      <c r="B285" s="34"/>
-      <c r="C285" s="62"/>
-      <c r="D285" s="34"/>
+      <c r="A285" s="33"/>
+      <c r="B285" s="33"/>
+      <c r="C285" s="56"/>
+      <c r="D285" s="33"/>
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A286" s="34"/>
-      <c r="B286" s="34"/>
-      <c r="C286" s="62"/>
-      <c r="D286" s="34"/>
+      <c r="A286" s="33"/>
+      <c r="B286" s="33"/>
+      <c r="C286" s="56"/>
+      <c r="D286" s="33"/>
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A287" s="34"/>
-      <c r="B287" s="34"/>
-      <c r="C287" s="62"/>
-      <c r="D287" s="34"/>
+      <c r="A287" s="33"/>
+      <c r="B287" s="33"/>
+      <c r="C287" s="56"/>
+      <c r="D287" s="33"/>
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A288" s="34"/>
-      <c r="B288" s="34"/>
-      <c r="C288" s="62"/>
-      <c r="D288" s="34"/>
+      <c r="A288" s="33"/>
+      <c r="B288" s="33"/>
+      <c r="C288" s="56"/>
+      <c r="D288" s="33"/>
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A289" s="34"/>
-      <c r="B289" s="34"/>
-      <c r="C289" s="62"/>
-      <c r="D289" s="34"/>
+      <c r="A289" s="33"/>
+      <c r="B289" s="33"/>
+      <c r="C289" s="56"/>
+      <c r="D289" s="33"/>
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A290" s="34"/>
-      <c r="B290" s="34"/>
-      <c r="C290" s="62"/>
-      <c r="D290" s="34"/>
+      <c r="A290" s="33"/>
+      <c r="B290" s="33"/>
+      <c r="C290" s="56"/>
+      <c r="D290" s="33"/>
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A291" s="34"/>
-      <c r="B291" s="34"/>
-      <c r="C291" s="35"/>
+      <c r="A291" s="33"/>
+      <c r="B291" s="33"/>
+      <c r="C291" s="34"/>
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="34"/>
-      <c r="B292" s="34"/>
-      <c r="C292" s="35"/>
+      <c r="A292" s="33"/>
+      <c r="B292" s="33"/>
+      <c r="C292" s="34"/>
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A293" s="34"/>
-      <c r="B293" s="34"/>
-      <c r="C293" s="35"/>
+      <c r="A293" s="33"/>
+      <c r="B293" s="33"/>
+      <c r="C293" s="34"/>
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A294" s="34"/>
-      <c r="B294" s="34"/>
-      <c r="C294" s="35"/>
+      <c r="A294" s="33"/>
+      <c r="B294" s="33"/>
+      <c r="C294" s="34"/>
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A295" s="34"/>
-      <c r="B295" s="34"/>
-      <c r="C295" s="35"/>
+      <c r="A295" s="33"/>
+      <c r="B295" s="33"/>
+      <c r="C295" s="34"/>
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A296" s="34"/>
-      <c r="B296" s="34"/>
-      <c r="C296" s="35"/>
+      <c r="A296" s="33"/>
+      <c r="B296" s="33"/>
+      <c r="C296" s="34"/>
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A297" s="34"/>
-      <c r="B297" s="34"/>
-      <c r="C297" s="35"/>
+      <c r="A297" s="33"/>
+      <c r="B297" s="33"/>
+      <c r="C297" s="34"/>
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A298" s="34"/>
-      <c r="B298" s="34"/>
-      <c r="C298" s="35"/>
+      <c r="A298" s="33"/>
+      <c r="B298" s="33"/>
+      <c r="C298" s="34"/>
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A299" s="34"/>
-      <c r="B299" s="34"/>
-      <c r="C299" s="35"/>
+      <c r="A299" s="33"/>
+      <c r="B299" s="33"/>
+      <c r="C299" s="34"/>
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C300" s="35"/>
+      <c r="C300" s="34"/>
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C301" s="35"/>
+      <c r="C301" s="34"/>
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C302" s="35"/>
+      <c r="C302" s="34"/>
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C303" s="35"/>
+      <c r="C303" s="34"/>
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C304" s="35"/>
+      <c r="C304" s="34"/>
     </row>
     <row r="305" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C305" s="35"/>
+      <c r="C305" s="34"/>
     </row>
     <row r="306" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C306" s="35"/>
+      <c r="C306" s="34"/>
     </row>
     <row r="307" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C307" s="35"/>
+      <c r="C307" s="34"/>
     </row>
     <row r="308" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C308" s="35"/>
+      <c r="C308" s="34"/>
     </row>
     <row r="309" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C309" s="35"/>
+      <c r="C309" s="34"/>
     </row>
     <row r="310" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C310" s="35"/>
+      <c r="C310" s="34"/>
     </row>
     <row r="311" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C311" s="35"/>
+      <c r="C311" s="34"/>
     </row>
     <row r="312" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C312" s="35"/>
+      <c r="C312" s="34"/>
     </row>
     <row r="313" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C313" s="35"/>
+      <c r="C313" s="34"/>
     </row>
     <row r="314" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C314" s="35"/>
+      <c r="C314" s="34"/>
     </row>
     <row r="315" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C315" s="35"/>
+      <c r="C315" s="34"/>
     </row>
     <row r="316" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C316" s="35"/>
+      <c r="C316" s="34"/>
     </row>
     <row r="317" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C317" s="35"/>
+      <c r="C317" s="34"/>
     </row>
     <row r="318" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C318" s="35"/>
+      <c r="C318" s="34"/>
     </row>
     <row r="319" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C319" s="35"/>
+      <c r="C319" s="34"/>
     </row>
     <row r="320" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C320" s="35"/>
+      <c r="C320" s="34"/>
     </row>
     <row r="321" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C321" s="35"/>
+      <c r="C321" s="34"/>
     </row>
     <row r="322" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C322" s="35"/>
+      <c r="C322" s="34"/>
     </row>
     <row r="323" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C323" s="35"/>
+      <c r="C323" s="34"/>
     </row>
     <row r="324" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C324" s="35"/>
+      <c r="C324" s="34"/>
     </row>
     <row r="325" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C325" s="35"/>
+      <c r="C325" s="34"/>
     </row>
     <row r="326" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C326" s="35"/>
+      <c r="C326" s="34"/>
     </row>
     <row r="327" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C327" s="35"/>
+      <c r="C327" s="34"/>
     </row>
     <row r="328" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C328" s="35"/>
+      <c r="C328" s="34"/>
     </row>
     <row r="329" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C329" s="35"/>
+      <c r="C329" s="34"/>
     </row>
     <row r="330" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C330" s="35"/>
+      <c r="C330" s="34"/>
     </row>
     <row r="331" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C331" s="35"/>
+      <c r="C331" s="34"/>
     </row>
     <row r="332" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C332" s="35"/>
+      <c r="C332" s="34"/>
     </row>
     <row r="333" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C333" s="35"/>
+      <c r="C333" s="34"/>
     </row>
     <row r="334" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C334" s="35"/>
+      <c r="C334" s="34"/>
     </row>
     <row r="335" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C335" s="35"/>
+      <c r="C335" s="34"/>
     </row>
     <row r="336" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C336" s="35"/>
+      <c r="C336" s="34"/>
     </row>
     <row r="337" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C337" s="35"/>
+      <c r="C337" s="34"/>
     </row>
     <row r="338" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C338" s="35"/>
+      <c r="C338" s="34"/>
     </row>
     <row r="339" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C339" s="35"/>
+      <c r="C339" s="34"/>
     </row>
     <row r="340" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C340" s="35"/>
+      <c r="C340" s="34"/>
     </row>
     <row r="341" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C341" s="35"/>
+      <c r="C341" s="34"/>
     </row>
     <row r="342" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C342" s="35"/>
+      <c r="C342" s="34"/>
     </row>
     <row r="343" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C343" s="35"/>
+      <c r="C343" s="34"/>
     </row>
     <row r="344" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C344" s="35"/>
+      <c r="C344" s="34"/>
     </row>
     <row r="345" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C345" s="35"/>
+      <c r="C345" s="34"/>
     </row>
     <row r="346" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C346" s="35"/>
+      <c r="C346" s="34"/>
     </row>
     <row r="347" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C347" s="35"/>
+      <c r="C347" s="34"/>
     </row>
     <row r="348" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C348" s="35"/>
+      <c r="C348" s="34"/>
     </row>
     <row r="349" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C349" s="35"/>
+      <c r="C349" s="34"/>
     </row>
     <row r="350" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C350" s="35"/>
+      <c r="C350" s="34"/>
     </row>
     <row r="351" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C351" s="35"/>
+      <c r="C351" s="34"/>
     </row>
     <row r="352" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C352" s="35"/>
+      <c r="C352" s="34"/>
     </row>
     <row r="353" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C353" s="35"/>
+      <c r="C353" s="34"/>
     </row>
     <row r="354" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C354" s="35"/>
+      <c r="C354" s="34"/>
     </row>
     <row r="355" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C355" s="35"/>
+      <c r="C355" s="34"/>
     </row>
     <row r="356" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C356" s="35"/>
+      <c r="C356" s="34"/>
     </row>
     <row r="357" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C357" s="35"/>
+      <c r="C357" s="34"/>
     </row>
     <row r="358" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C358" s="35"/>
+      <c r="C358" s="34"/>
     </row>
     <row r="359" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C359" s="35"/>
+      <c r="C359" s="34"/>
     </row>
     <row r="360" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C360" s="35"/>
+      <c r="C360" s="34"/>
     </row>
     <row r="361" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C361" s="35"/>
+      <c r="C361" s="34"/>
     </row>
     <row r="362" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C362" s="35"/>
+      <c r="C362" s="34"/>
     </row>
     <row r="363" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C363" s="35"/>
+      <c r="C363" s="34"/>
     </row>
     <row r="364" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C364" s="35"/>
+      <c r="C364" s="34"/>
     </row>
     <row r="365" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C365" s="35"/>
+      <c r="C365" s="34"/>
     </row>
     <row r="366" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C366" s="35"/>
+      <c r="C366" s="34"/>
     </row>
     <row r="367" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C367" s="35"/>
+      <c r="C367" s="34"/>
     </row>
     <row r="368" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C368" s="35"/>
+      <c r="C368" s="34"/>
     </row>
     <row r="369" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C369" s="35"/>
+      <c r="C369" s="34"/>
     </row>
     <row r="370" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C370" s="35"/>
+      <c r="C370" s="34"/>
     </row>
     <row r="371" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C371" s="35"/>
+      <c r="C371" s="34"/>
     </row>
     <row r="372" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C372" s="35"/>
+      <c r="C372" s="34"/>
     </row>
     <row r="373" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C373" s="35"/>
+      <c r="C373" s="34"/>
     </row>
     <row r="374" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C374" s="35"/>
+      <c r="C374" s="34"/>
     </row>
     <row r="375" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C375" s="35"/>
+      <c r="C375" s="34"/>
     </row>
     <row r="376" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C376" s="35"/>
+      <c r="C376" s="34"/>
     </row>
     <row r="377" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C377" s="35"/>
+      <c r="C377" s="34"/>
     </row>
     <row r="378" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C378" s="35"/>
+      <c r="C378" s="34"/>
     </row>
     <row r="379" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C379" s="35"/>
+      <c r="C379" s="34"/>
     </row>
     <row r="380" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C380" s="35"/>
+      <c r="C380" s="34"/>
     </row>
     <row r="381" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C381" s="35"/>
+      <c r="C381" s="34"/>
     </row>
     <row r="382" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C382" s="35"/>
+      <c r="C382" s="34"/>
     </row>
     <row r="383" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C383" s="35"/>
+      <c r="C383" s="34"/>
     </row>
     <row r="384" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C384" s="35"/>
+      <c r="C384" s="34"/>
     </row>
     <row r="385" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C385" s="35"/>
+      <c r="C385" s="34"/>
     </row>
     <row r="386" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C386" s="35"/>
+      <c r="C386" s="34"/>
     </row>
     <row r="387" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C387" s="35"/>
+      <c r="C387" s="34"/>
     </row>
     <row r="388" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C388" s="35"/>
+      <c r="C388" s="34"/>
     </row>
     <row r="389" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C389" s="35"/>
+      <c r="C389" s="34"/>
     </row>
     <row r="390" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C390" s="35"/>
+      <c r="C390" s="34"/>
     </row>
     <row r="391" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C391" s="35"/>
+      <c r="C391" s="34"/>
     </row>
     <row r="392" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C392" s="35"/>
+      <c r="C392" s="34"/>
     </row>
     <row r="393" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C393" s="35"/>
+      <c r="C393" s="34"/>
     </row>
     <row r="394" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C394" s="35"/>
+      <c r="C394" s="34"/>
     </row>
     <row r="395" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C395" s="35"/>
+      <c r="C395" s="34"/>
     </row>
     <row r="396" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C396" s="35"/>
+      <c r="C396" s="34"/>
     </row>
     <row r="397" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C397" s="35"/>
+      <c r="C397" s="34"/>
     </row>
     <row r="398" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C398" s="35"/>
+      <c r="C398" s="34"/>
     </row>
     <row r="399" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C399" s="35"/>
+      <c r="C399" s="34"/>
     </row>
     <row r="400" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C400" s="35"/>
+      <c r="C400" s="34"/>
     </row>
     <row r="401" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C401" s="35"/>
+      <c r="C401" s="34"/>
     </row>
     <row r="402" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C402" s="35"/>
+      <c r="C402" s="34"/>
     </row>
     <row r="403" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C403" s="35"/>
+      <c r="C403" s="34"/>
     </row>
     <row r="404" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C404" s="35"/>
+      <c r="C404" s="34"/>
     </row>
     <row r="405" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C405" s="35"/>
+      <c r="C405" s="34"/>
     </row>
     <row r="406" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C406" s="35"/>
+      <c r="C406" s="34"/>
     </row>
     <row r="407" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C407" s="35"/>
+      <c r="C407" s="34"/>
     </row>
     <row r="408" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C408" s="35"/>
+      <c r="C408" s="34"/>
     </row>
     <row r="409" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C409" s="35"/>
+      <c r="C409" s="34"/>
     </row>
     <row r="410" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C410" s="35"/>
+      <c r="C410" s="34"/>
     </row>
     <row r="411" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C411" s="35"/>
+      <c r="C411" s="34"/>
     </row>
     <row r="412" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C412" s="35"/>
+      <c r="C412" s="34"/>
     </row>
     <row r="413" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C413" s="35"/>
+      <c r="C413" s="34"/>
     </row>
     <row r="414" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C414" s="35"/>
+      <c r="C414" s="34"/>
     </row>
     <row r="415" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C415" s="35"/>
+      <c r="C415" s="34"/>
     </row>
     <row r="416" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C416" s="35"/>
+      <c r="C416" s="34"/>
     </row>
     <row r="417" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C417" s="35"/>
+      <c r="C417" s="34"/>
     </row>
     <row r="418" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C418" s="35"/>
+      <c r="C418" s="34"/>
     </row>
     <row r="419" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C419" s="35"/>
+      <c r="C419" s="34"/>
     </row>
     <row r="420" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C420" s="35"/>
+      <c r="C420" s="34"/>
     </row>
     <row r="421" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C421" s="35"/>
+      <c r="C421" s="34"/>
     </row>
     <row r="422" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C422" s="35"/>
+      <c r="C422" s="34"/>
     </row>
     <row r="423" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C423" s="35"/>
+      <c r="C423" s="34"/>
     </row>
     <row r="424" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C424" s="35"/>
+      <c r="C424" s="34"/>
     </row>
     <row r="425" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C425" s="35"/>
+      <c r="C425" s="34"/>
     </row>
     <row r="426" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C426" s="35"/>
+      <c r="C426" s="34"/>
     </row>
     <row r="427" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C427" s="35"/>
+      <c r="C427" s="34"/>
     </row>
     <row r="428" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C428" s="35"/>
+      <c r="C428" s="34"/>
     </row>
     <row r="429" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C429" s="35"/>
+      <c r="C429" s="34"/>
     </row>
     <row r="430" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C430" s="35"/>
+      <c r="C430" s="34"/>
     </row>
     <row r="431" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C431" s="35"/>
+      <c r="C431" s="34"/>
     </row>
     <row r="432" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C432" s="35"/>
+      <c r="C432" s="34"/>
     </row>
     <row r="433" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C433" s="35"/>
+      <c r="C433" s="34"/>
     </row>
     <row r="434" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C434" s="35"/>
+      <c r="C434" s="34"/>
     </row>
     <row r="435" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C435" s="35"/>
+      <c r="C435" s="34"/>
     </row>
     <row r="436" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C436" s="35"/>
+      <c r="C436" s="34"/>
     </row>
     <row r="437" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C437" s="35"/>
+      <c r="C437" s="34"/>
     </row>
     <row r="438" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C438" s="35"/>
+      <c r="C438" s="34"/>
     </row>
     <row r="439" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C439" s="35"/>
+      <c r="C439" s="34"/>
     </row>
     <row r="440" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C440" s="35"/>
+      <c r="C440" s="34"/>
     </row>
     <row r="441" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C441" s="35"/>
+      <c r="C441" s="34"/>
     </row>
     <row r="442" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C442" s="35"/>
+      <c r="C442" s="34"/>
     </row>
     <row r="443" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C443" s="35"/>
+      <c r="C443" s="34"/>
     </row>
     <row r="444" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C444" s="35"/>
+      <c r="C444" s="34"/>
     </row>
     <row r="445" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C445" s="35"/>
+      <c r="C445" s="34"/>
     </row>
     <row r="446" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C446" s="35"/>
+      <c r="C446" s="34"/>
     </row>
     <row r="447" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C447" s="35"/>
+      <c r="C447" s="34"/>
     </row>
     <row r="448" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C448" s="35"/>
+      <c r="C448" s="34"/>
     </row>
     <row r="449" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C449" s="35"/>
+      <c r="C449" s="34"/>
     </row>
     <row r="450" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C450" s="35"/>
+      <c r="C450" s="34"/>
     </row>
     <row r="451" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C451" s="35"/>
+      <c r="C451" s="34"/>
     </row>
     <row r="452" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C452" s="35"/>
+      <c r="C452" s="34"/>
     </row>
     <row r="453" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C453" s="35"/>
+      <c r="C453" s="34"/>
     </row>
     <row r="454" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C454" s="35"/>
+      <c r="C454" s="34"/>
     </row>
     <row r="455" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C455" s="35"/>
+      <c r="C455" s="34"/>
     </row>
     <row r="456" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C456" s="35"/>
+      <c r="C456" s="34"/>
     </row>
     <row r="457" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C457" s="35"/>
+      <c r="C457" s="34"/>
     </row>
     <row r="458" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C458" s="35"/>
+      <c r="C458" s="34"/>
     </row>
     <row r="459" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C459" s="35"/>
+      <c r="C459" s="34"/>
     </row>
     <row r="460" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C460" s="35"/>
+      <c r="C460" s="34"/>
     </row>
     <row r="461" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C461" s="35"/>
+      <c r="C461" s="34"/>
     </row>
     <row r="462" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C462" s="35"/>
+      <c r="C462" s="34"/>
     </row>
     <row r="463" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C463" s="35"/>
+      <c r="C463" s="34"/>
     </row>
     <row r="464" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C464" s="35"/>
+      <c r="C464" s="34"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:C18">
@@ -6850,19 +6878,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -6870,16 +6898,16 @@
         <v>14</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="E2" s="29" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -6887,16 +6915,16 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="C3" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -6904,20 +6932,21 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="C4" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="E4" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -6937,16 +6966,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="D1" s="17" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -6954,7 +6983,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
@@ -6965,34 +6994,34 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -7014,25 +7043,25 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -7060,594 +7089,594 @@
         <v>9</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="22" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="22" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="22" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="22" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="22" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="22" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="C8" s="23"/>
     </row>
     <row r="9" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="22" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="C9" s="23"/>
     </row>
     <row r="10" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="22" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="C10" s="23"/>
     </row>
     <row r="11" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="22" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="22" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="C12" s="23"/>
     </row>
     <row r="13" spans="1:3" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="22" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="22" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="22" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="22" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="22" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="22" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="22" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="C19" s="23"/>
     </row>
     <row r="20" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="18" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="C20" s="23"/>
     </row>
     <row r="21" spans="1:3" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="22" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="C21" s="23"/>
     </row>
     <row r="22" spans="1:3" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="18" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="C22" s="23"/>
     </row>
     <row r="23" spans="1:3" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="22" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="22" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="22" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="22" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="22" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="22" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="22" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="22" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="22" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="52.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="18" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="22" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="27" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="C34" s="28" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="27" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="27" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="C36" s="28"/>
     </row>
     <row r="37" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="31" t="s">
-        <v>50</v>
+      <c r="A37" s="30" t="s">
+        <v>47</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="C37" s="23"/>
     </row>
     <row r="38" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="27" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="C38" s="28"/>
     </row>
     <row r="39" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="22" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="C39" s="23"/>
     </row>
     <row r="40" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="22" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B40" s="22" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="C40" s="23"/>
     </row>
     <row r="41" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="22" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="C41" s="23"/>
     </row>
     <row r="42" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="27" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="C42" s="28"/>
     </row>
     <row r="43" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="22" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="C43" s="23"/>
     </row>
     <row r="44" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="22" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="C44" s="23"/>
     </row>
     <row r="45" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="22" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="C45" s="23"/>
     </row>
     <row r="46" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="22" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="C46" s="23"/>
     </row>
     <row r="47" spans="1:3" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="27" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="C47" s="28"/>
     </row>
     <row r="48" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="22" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="B48" s="22" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="C48" s="23"/>
     </row>
     <row r="49" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="22" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="C49" s="23"/>
     </row>
     <row r="50" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="27" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="B50" s="27" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="C50" s="28"/>
     </row>
     <row r="51" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="27" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="C51" s="28"/>
     </row>
     <row r="52" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="22" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="B52" s="22" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="C52" s="23"/>
     </row>
     <row r="53" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="27" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="C53" s="28"/>
     </row>
     <row r="54" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="22" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="C54" s="23"/>
     </row>
     <row r="55" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="27" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="C55" s="28"/>
     </row>
     <row r="56" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="27" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B56" s="27" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="C56" s="28"/>
     </row>
     <row r="57" spans="1:3" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="27" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="C57" s="28"/>
     </row>
     <row r="58" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="27" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="C58" s="28"/>
     </row>
     <row r="59" spans="1:3" ht="34" x14ac:dyDescent="0.2">
-      <c r="A59" s="37" t="s">
-        <v>120</v>
-      </c>
-      <c r="B59" s="37" t="s">
-        <v>395</v>
-      </c>
-      <c r="C59" s="38"/>
+      <c r="A59" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="B59" s="36" t="s">
+        <v>383</v>
+      </c>
+      <c r="C59" s="37"/>
     </row>
     <row r="60" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A60" s="37" t="s">
-        <v>403</v>
-      </c>
-      <c r="B60" s="37" t="s">
-        <v>404</v>
-      </c>
-      <c r="C60" s="38"/>
+      <c r="A60" s="36" t="s">
+        <v>391</v>
+      </c>
+      <c r="B60" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="C60" s="37"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C53" xr:uid="{D95B3E19-31EE-401E-8E14-DBEF7BC74F95}"/>
@@ -7669,42 +7698,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="B2" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B4" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -7726,18 +7755,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="B2" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -7765,135 +7794,135 @@
         <v>4</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B3" s="32" t="s">
-        <v>385</v>
+        <v>105</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="B4" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="B5" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="16" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="B7" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="B15" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/images/stx_fish_image_schema_main_v0.1.xlsx
+++ b/images/stx_fish_image_schema_main_v0.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/providen/Documents/EI/Projects/COPO-schemas/images/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D215CBE6-07FA-1D44-8A6B-A6890E63F3B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F37A50B-A3A7-CB49-B686-660649BABCF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32740" yWindow="-940" windowWidth="30240" windowHeight="17900" xr2:uid="{7BD8D0E6-E1F4-E04F-9790-31602B31B6DB}"/>
+    <workbookView xWindow="37500" yWindow="-320" windowWidth="30240" windowHeight="17900" activeTab="3" xr2:uid="{7BD8D0E6-E1F4-E04F-9790-31602B31B6DB}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="413">
   <si>
     <t>component_name</t>
   </si>
@@ -6985,9 +6985,6 @@
       <c r="B2" t="s">
         <v>240</v>
       </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
       <c r="D2" t="s">
         <v>17</v>
       </c>
